--- a/data/macro/USA/US Unemployment rate.xlsx
+++ b/data/macro/USA/US Unemployment rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521AE3A0-F011-4BC3-82E7-A7D323ED5070}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E330717-4DF3-45FB-A48A-1DDC9D06BD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
   </bookViews>
   <sheets>
     <sheet name="USURTOT" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -62,14 +62,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.investing.com/economic-calendar/unemployment-rate-300</t>
-  </si>
-  <si>
     <t>frequency</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Monthly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/unemployment-rate-300</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -84,7 +85,7 @@
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -126,6 +127,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -144,15 +153,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -192,10 +204,14 @@
     <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6033,6 +6049,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6040,7 +6057,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6966,18 +6982,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937CB4E7-01E8-4116-8C39-2B0211A5B043}">
-  <dimension ref="A1:H938"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H939"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="5"/>
+    <col min="5" max="7" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -7000,7 +7016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>17533</v>
       </c>
@@ -7017,7 +7033,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17564</v>
       </c>
@@ -7037,7 +7053,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>17593</v>
       </c>
@@ -7057,7 +7073,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>17624</v>
       </c>
@@ -7077,7 +7093,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>17654</v>
       </c>
@@ -7097,7 +7113,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>17685</v>
       </c>
@@ -7117,7 +7133,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>17715</v>
       </c>
@@ -7137,7 +7153,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>17746</v>
       </c>
@@ -7157,7 +7173,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>17777</v>
       </c>
@@ -7177,7 +7193,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>17807</v>
       </c>
@@ -7197,7 +7213,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>17838</v>
       </c>
@@ -7217,7 +7233,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>17868</v>
       </c>
@@ -7237,7 +7253,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>17899</v>
       </c>
@@ -7257,7 +7273,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>17930</v>
       </c>
@@ -7277,7 +7293,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>17958</v>
       </c>
@@ -7297,7 +7313,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17989</v>
       </c>
@@ -7317,7 +7333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18019</v>
       </c>
@@ -7337,7 +7353,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>18050</v>
       </c>
@@ -7357,7 +7373,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>18080</v>
       </c>
@@ -7377,7 +7393,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>18111</v>
       </c>
@@ -7397,7 +7413,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>18142</v>
       </c>
@@ -7417,7 +7433,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>18172</v>
       </c>
@@ -7437,7 +7453,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>18203</v>
       </c>
@@ -7457,7 +7473,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>18233</v>
       </c>
@@ -7477,7 +7493,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>18264</v>
       </c>
@@ -7497,7 +7513,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>18295</v>
       </c>
@@ -7517,7 +7533,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>18323</v>
       </c>
@@ -7537,7 +7553,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>18354</v>
       </c>
@@ -7557,7 +7573,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>18384</v>
       </c>
@@ -7577,7 +7593,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>18415</v>
       </c>
@@ -7597,7 +7613,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>18445</v>
       </c>
@@ -7617,7 +7633,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>18476</v>
       </c>
@@ -7637,7 +7653,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>18507</v>
       </c>
@@ -7657,7 +7673,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>18537</v>
       </c>
@@ -7677,7 +7693,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>18568</v>
       </c>
@@ -7697,7 +7713,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>18598</v>
       </c>
@@ -7717,7 +7733,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>18629</v>
       </c>
@@ -7737,7 +7753,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>18660</v>
       </c>
@@ -7757,7 +7773,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>18688</v>
       </c>
@@ -7777,7 +7793,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>18719</v>
       </c>
@@ -7797,7 +7813,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>18749</v>
       </c>
@@ -7817,7 +7833,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>18780</v>
       </c>
@@ -7837,7 +7853,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>18810</v>
       </c>
@@ -7857,7 +7873,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>18841</v>
       </c>
@@ -7877,7 +7893,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>18872</v>
       </c>
@@ -7897,7 +7913,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>18902</v>
       </c>
@@ -7917,7 +7933,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>18933</v>
       </c>
@@ -7937,7 +7953,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>18963</v>
       </c>
@@ -7957,7 +7973,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>18994</v>
       </c>
@@ -7977,7 +7993,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>19025</v>
       </c>
@@ -7997,7 +8013,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>19054</v>
       </c>
@@ -8017,7 +8033,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>19085</v>
       </c>
@@ -8037,7 +8053,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>19115</v>
       </c>
@@ -8057,7 +8073,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>19146</v>
       </c>
@@ -8077,7 +8093,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>19176</v>
       </c>
@@ -8097,7 +8113,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>19207</v>
       </c>
@@ -8117,7 +8133,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>19238</v>
       </c>
@@ -8137,7 +8153,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>19268</v>
       </c>
@@ -8157,7 +8173,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>19299</v>
       </c>
@@ -8177,7 +8193,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>19329</v>
       </c>
@@ -8197,7 +8213,7 @@
         <v>2.7999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>19360</v>
       </c>
@@ -8217,7 +8233,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>19391</v>
       </c>
@@ -8237,7 +8253,7 @@
         <v>2.8999999999999998E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>19419</v>
       </c>
@@ -8257,7 +8273,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>19450</v>
       </c>
@@ -8277,7 +8293,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>19480</v>
       </c>
@@ -8297,7 +8313,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>19511</v>
       </c>
@@ -8317,7 +8333,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>19541</v>
       </c>
@@ -8337,7 +8353,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>19572</v>
       </c>
@@ -8357,7 +8373,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>19603</v>
       </c>
@@ -8377,7 +8393,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>19633</v>
       </c>
@@ -8397,7 +8413,7 @@
         <v>2.8999999999999998E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>19664</v>
       </c>
@@ -8417,7 +8433,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>19694</v>
       </c>
@@ -8437,7 +8453,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>19725</v>
       </c>
@@ -8457,7 +8473,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>19756</v>
       </c>
@@ -8477,7 +8493,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>19784</v>
       </c>
@@ -8497,7 +8513,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>19815</v>
       </c>
@@ -8517,7 +8533,7 @@
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>19845</v>
       </c>
@@ -8537,7 +8553,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>19876</v>
       </c>
@@ -8557,7 +8573,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>19906</v>
       </c>
@@ -8577,7 +8593,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>19937</v>
       </c>
@@ -8597,7 +8613,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>19968</v>
       </c>
@@ -8617,7 +8633,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>19998</v>
       </c>
@@ -8637,7 +8653,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>20029</v>
       </c>
@@ -8657,7 +8673,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>20059</v>
       </c>
@@ -8677,7 +8693,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>20090</v>
       </c>
@@ -8697,7 +8713,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>20121</v>
       </c>
@@ -8717,7 +8733,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>20149</v>
       </c>
@@ -8737,7 +8753,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>20180</v>
       </c>
@@ -8757,7 +8773,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>20210</v>
       </c>
@@ -8777,7 +8793,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>20241</v>
       </c>
@@ -8797,7 +8813,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>20271</v>
       </c>
@@ -8817,7 +8833,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>20302</v>
       </c>
@@ -8837,7 +8853,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>20333</v>
       </c>
@@ -8857,7 +8873,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>20363</v>
       </c>
@@ -8877,7 +8893,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>20394</v>
       </c>
@@ -8897,7 +8913,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>20424</v>
       </c>
@@ -8917,7 +8933,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>20455</v>
       </c>
@@ -8937,7 +8953,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>20486</v>
       </c>
@@ -8957,7 +8973,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>20515</v>
       </c>
@@ -8977,7 +8993,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>20546</v>
       </c>
@@ -8997,7 +9013,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>20576</v>
       </c>
@@ -9017,7 +9033,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>20607</v>
       </c>
@@ -9037,7 +9053,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>20637</v>
       </c>
@@ -9057,7 +9073,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>20668</v>
       </c>
@@ -9077,7 +9093,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>20699</v>
       </c>
@@ -9097,7 +9113,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>20729</v>
       </c>
@@ -9117,7 +9133,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>20760</v>
       </c>
@@ -9137,7 +9153,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>20790</v>
       </c>
@@ -9157,7 +9173,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>20821</v>
       </c>
@@ -9177,7 +9193,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>20852</v>
       </c>
@@ -9197,7 +9213,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>20880</v>
       </c>
@@ -9217,7 +9233,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>20911</v>
       </c>
@@ -9237,7 +9253,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>20941</v>
       </c>
@@ -9257,7 +9273,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>20972</v>
       </c>
@@ -9277,7 +9293,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>21002</v>
       </c>
@@ -9297,7 +9313,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>21033</v>
       </c>
@@ -9317,7 +9333,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>21064</v>
       </c>
@@ -9337,7 +9353,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>21094</v>
       </c>
@@ -9357,7 +9373,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>21125</v>
       </c>
@@ -9377,7 +9393,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>21155</v>
       </c>
@@ -9397,7 +9413,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>21186</v>
       </c>
@@ -9417,7 +9433,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>21217</v>
       </c>
@@ -9437,7 +9453,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>21245</v>
       </c>
@@ -9457,7 +9473,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>21276</v>
       </c>
@@ -9477,7 +9493,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>21306</v>
       </c>
@@ -9497,7 +9513,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>21337</v>
       </c>
@@ -9517,7 +9533,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>21367</v>
       </c>
@@ -9537,7 +9553,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>21398</v>
       </c>
@@ -9557,7 +9573,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>21429</v>
       </c>
@@ -9577,7 +9593,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>21459</v>
       </c>
@@ -9597,7 +9613,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>21490</v>
       </c>
@@ -9617,7 +9633,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>21520</v>
       </c>
@@ -9637,7 +9653,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>21551</v>
       </c>
@@ -9657,7 +9673,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>21582</v>
       </c>
@@ -9677,7 +9693,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>21610</v>
       </c>
@@ -9697,7 +9713,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>21641</v>
       </c>
@@ -9717,7 +9733,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>21671</v>
       </c>
@@ -9737,7 +9753,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>21702</v>
       </c>
@@ -9757,7 +9773,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>21732</v>
       </c>
@@ -9777,7 +9793,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>21763</v>
       </c>
@@ -9797,7 +9813,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>21794</v>
       </c>
@@ -9817,7 +9833,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>21824</v>
       </c>
@@ -9837,7 +9853,7 @@
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>21855</v>
       </c>
@@ -9857,7 +9873,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>21885</v>
       </c>
@@ -9877,7 +9893,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>21916</v>
       </c>
@@ -9897,7 +9913,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>21947</v>
       </c>
@@ -9917,7 +9933,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>21976</v>
       </c>
@@ -9937,7 +9953,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>22007</v>
       </c>
@@ -9957,7 +9973,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>22037</v>
       </c>
@@ -9977,7 +9993,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>22068</v>
       </c>
@@ -9997,7 +10013,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>22098</v>
       </c>
@@ -10017,7 +10033,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>22129</v>
       </c>
@@ -10037,7 +10053,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>22160</v>
       </c>
@@ -10057,7 +10073,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>22190</v>
       </c>
@@ -10077,7 +10093,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>22221</v>
       </c>
@@ -10097,7 +10113,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>22251</v>
       </c>
@@ -10117,7 +10133,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>22282</v>
       </c>
@@ -10137,7 +10153,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>22313</v>
       </c>
@@ -10157,7 +10173,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>22341</v>
       </c>
@@ -10177,7 +10193,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>22372</v>
       </c>
@@ -10197,7 +10213,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>22402</v>
       </c>
@@ -10217,7 +10233,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>22433</v>
       </c>
@@ -10237,7 +10253,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>22463</v>
       </c>
@@ -10257,7 +10273,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>22494</v>
       </c>
@@ -10277,7 +10293,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>22525</v>
       </c>
@@ -10297,7 +10313,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>22555</v>
       </c>
@@ -10317,7 +10333,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>22586</v>
       </c>
@@ -10337,7 +10353,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>22616</v>
       </c>
@@ -10357,7 +10373,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>22647</v>
       </c>
@@ -10377,7 +10393,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>22678</v>
       </c>
@@ -10397,7 +10413,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>22706</v>
       </c>
@@ -10417,7 +10433,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>22737</v>
       </c>
@@ -10437,7 +10453,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>22767</v>
       </c>
@@ -10457,7 +10473,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>22798</v>
       </c>
@@ -10477,7 +10493,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>22828</v>
       </c>
@@ -10497,7 +10513,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>22859</v>
       </c>
@@ -10517,7 +10533,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>22890</v>
       </c>
@@ -10537,7 +10553,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>22920</v>
       </c>
@@ -10557,7 +10573,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>22951</v>
       </c>
@@ -10577,7 +10593,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>22981</v>
       </c>
@@ -10597,7 +10613,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>23012</v>
       </c>
@@ -10617,7 +10633,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>23043</v>
       </c>
@@ -10637,7 +10653,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>23071</v>
       </c>
@@ -10657,7 +10673,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>23102</v>
       </c>
@@ -10677,7 +10693,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>23132</v>
       </c>
@@ -10697,7 +10713,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>23163</v>
       </c>
@@ -10717,7 +10733,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>23193</v>
       </c>
@@ -10737,7 +10753,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>23224</v>
       </c>
@@ -10757,7 +10773,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>23255</v>
       </c>
@@ -10777,7 +10793,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>23285</v>
       </c>
@@ -10797,7 +10813,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>23316</v>
       </c>
@@ -10817,7 +10833,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>23346</v>
       </c>
@@ -10837,7 +10853,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>23377</v>
       </c>
@@ -10857,7 +10873,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>23408</v>
       </c>
@@ -10877,7 +10893,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>23437</v>
       </c>
@@ -10897,7 +10913,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>23468</v>
       </c>
@@ -10917,7 +10933,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>23498</v>
       </c>
@@ -10937,7 +10953,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>23529</v>
       </c>
@@ -10957,7 +10973,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>23559</v>
       </c>
@@ -10977,7 +10993,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>23590</v>
       </c>
@@ -10997,7 +11013,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>23621</v>
       </c>
@@ -11017,7 +11033,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>23651</v>
       </c>
@@ -11037,7 +11053,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>23682</v>
       </c>
@@ -11057,7 +11073,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>23712</v>
       </c>
@@ -11077,7 +11093,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>23743</v>
       </c>
@@ -11097,7 +11113,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>23774</v>
       </c>
@@ -11117,7 +11133,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>23802</v>
       </c>
@@ -11137,7 +11153,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>23833</v>
       </c>
@@ -11157,7 +11173,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>23863</v>
       </c>
@@ -11177,7 +11193,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>23894</v>
       </c>
@@ -11197,7 +11213,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>23924</v>
       </c>
@@ -11217,7 +11233,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>23955</v>
       </c>
@@ -11237,7 +11253,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>23986</v>
       </c>
@@ -11257,7 +11273,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>24016</v>
       </c>
@@ -11277,7 +11293,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>24047</v>
       </c>
@@ -11297,7 +11313,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>24077</v>
       </c>
@@ -11317,7 +11333,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>24108</v>
       </c>
@@ -11337,7 +11353,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>24139</v>
       </c>
@@ -11357,7 +11373,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>24167</v>
       </c>
@@ -11377,7 +11393,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>24198</v>
       </c>
@@ -11397,7 +11413,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>24228</v>
       </c>
@@ -11417,7 +11433,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>24259</v>
       </c>
@@ -11437,7 +11453,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>24289</v>
       </c>
@@ -11457,7 +11473,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>24320</v>
       </c>
@@ -11477,7 +11493,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>24351</v>
       </c>
@@ -11497,7 +11513,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>24381</v>
       </c>
@@ -11517,7 +11533,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>24412</v>
       </c>
@@ -11537,7 +11553,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>24442</v>
       </c>
@@ -11557,7 +11573,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>24473</v>
       </c>
@@ -11577,7 +11593,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>24504</v>
       </c>
@@ -11597,7 +11613,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>24532</v>
       </c>
@@ -11617,7 +11633,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>24563</v>
       </c>
@@ -11637,7 +11653,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>24593</v>
       </c>
@@ -11657,7 +11673,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>24624</v>
       </c>
@@ -11677,7 +11693,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>24654</v>
       </c>
@@ -11697,7 +11713,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>24685</v>
       </c>
@@ -11717,7 +11733,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>24716</v>
       </c>
@@ -11737,7 +11753,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>24746</v>
       </c>
@@ -11757,7 +11773,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>24777</v>
       </c>
@@ -11777,7 +11793,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>24807</v>
       </c>
@@ -11797,7 +11813,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>24838</v>
       </c>
@@ -11817,7 +11833,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>24869</v>
       </c>
@@ -11837,7 +11853,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>24898</v>
       </c>
@@ -11857,7 +11873,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>24929</v>
       </c>
@@ -11877,7 +11893,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>24959</v>
       </c>
@@ -11897,7 +11913,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>24990</v>
       </c>
@@ -11917,7 +11933,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>25020</v>
       </c>
@@ -11937,7 +11953,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>25051</v>
       </c>
@@ -11957,7 +11973,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>25082</v>
       </c>
@@ -11977,7 +11993,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>25112</v>
       </c>
@@ -11997,7 +12013,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>25143</v>
       </c>
@@ -12017,7 +12033,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>25173</v>
       </c>
@@ -12037,7 +12053,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>25204</v>
       </c>
@@ -12057,7 +12073,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>25235</v>
       </c>
@@ -12077,7 +12093,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>25263</v>
       </c>
@@ -12097,7 +12113,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>25294</v>
       </c>
@@ -12117,7 +12133,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>25324</v>
       </c>
@@ -12137,7 +12153,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>25355</v>
       </c>
@@ -12157,7 +12173,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>25385</v>
       </c>
@@ -12177,7 +12193,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>25416</v>
       </c>
@@ -12197,7 +12213,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>25447</v>
       </c>
@@ -12217,7 +12233,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>25477</v>
       </c>
@@ -12237,7 +12253,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>25508</v>
       </c>
@@ -12257,7 +12273,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" s="7">
         <v>25538</v>
       </c>
@@ -12278,7 +12294,7 @@
       </c>
       <c r="H265" s="10"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" s="7">
         <v>25569</v>
       </c>
@@ -12299,7 +12315,7 @@
       </c>
       <c r="H266" s="10"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" s="7">
         <v>25600</v>
       </c>
@@ -12320,7 +12336,7 @@
       </c>
       <c r="H267" s="10"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" s="7">
         <v>25628</v>
       </c>
@@ -12341,7 +12357,7 @@
       </c>
       <c r="H268" s="10"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" s="7">
         <v>25659</v>
       </c>
@@ -12362,7 +12378,7 @@
       </c>
       <c r="H269" s="10"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" s="7">
         <v>25689</v>
       </c>
@@ -12383,7 +12399,7 @@
       </c>
       <c r="H270" s="10"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" s="7">
         <v>25720</v>
       </c>
@@ -12404,7 +12420,7 @@
       </c>
       <c r="H271" s="10"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" s="7">
         <v>25750</v>
       </c>
@@ -12425,7 +12441,7 @@
       </c>
       <c r="H272" s="10"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" s="7">
         <v>25781</v>
       </c>
@@ -12446,7 +12462,7 @@
       </c>
       <c r="H273" s="10"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" s="7">
         <v>25812</v>
       </c>
@@ -12467,7 +12483,7 @@
       </c>
       <c r="H274" s="10"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" s="7">
         <v>25842</v>
       </c>
@@ -12488,7 +12504,7 @@
       </c>
       <c r="H275" s="10"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" s="7">
         <v>25873</v>
       </c>
@@ -12509,7 +12525,7 @@
       </c>
       <c r="H276" s="10"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" s="7">
         <v>25903</v>
       </c>
@@ -12530,7 +12546,7 @@
       </c>
       <c r="H277" s="10"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" s="7">
         <v>25934</v>
       </c>
@@ -12551,7 +12567,7 @@
       </c>
       <c r="H278" s="10"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279" s="7">
         <v>25965</v>
       </c>
@@ -12572,7 +12588,7 @@
       </c>
       <c r="H279" s="10"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" s="7">
         <v>25993</v>
       </c>
@@ -12593,7 +12609,7 @@
       </c>
       <c r="H280" s="10"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" s="7">
         <v>26024</v>
       </c>
@@ -12614,7 +12630,7 @@
       </c>
       <c r="H281" s="10"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" s="7">
         <v>26054</v>
       </c>
@@ -12635,7 +12651,7 @@
       </c>
       <c r="H282" s="10"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" s="7">
         <v>26085</v>
       </c>
@@ -12656,7 +12672,7 @@
       </c>
       <c r="H283" s="10"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" s="7">
         <v>26115</v>
       </c>
@@ -12677,7 +12693,7 @@
       </c>
       <c r="H284" s="10"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" s="7">
         <v>26146</v>
       </c>
@@ -12698,7 +12714,7 @@
       </c>
       <c r="H285" s="10"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" s="7">
         <v>26177</v>
       </c>
@@ -12719,7 +12735,7 @@
       </c>
       <c r="H286" s="10"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" s="7">
         <v>26207</v>
       </c>
@@ -12740,7 +12756,7 @@
       </c>
       <c r="H287" s="10"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" s="7">
         <v>26238</v>
       </c>
@@ -12761,7 +12777,7 @@
       </c>
       <c r="H288" s="10"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289" s="7">
         <v>26268</v>
       </c>
@@ -12782,7 +12798,7 @@
       </c>
       <c r="H289" s="10"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" s="7">
         <v>26299</v>
       </c>
@@ -12803,7 +12819,7 @@
       </c>
       <c r="H290" s="10"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291" s="7">
         <v>26330</v>
       </c>
@@ -12824,7 +12840,7 @@
       </c>
       <c r="H291" s="10"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292" s="7">
         <v>26359</v>
       </c>
@@ -12845,7 +12861,7 @@
       </c>
       <c r="H292" s="10"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293" s="7">
         <v>26390</v>
       </c>
@@ -12866,7 +12882,7 @@
       </c>
       <c r="H293" s="10"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294" s="7">
         <v>26420</v>
       </c>
@@ -12887,7 +12903,7 @@
       </c>
       <c r="H294" s="10"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295" s="7">
         <v>26451</v>
       </c>
@@ -12908,7 +12924,7 @@
       </c>
       <c r="H295" s="10"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296" s="7">
         <v>26481</v>
       </c>
@@ -12929,7 +12945,7 @@
       </c>
       <c r="H296" s="10"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A297" s="7">
         <v>26512</v>
       </c>
@@ -12950,7 +12966,7 @@
       </c>
       <c r="H297" s="10"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298" s="7">
         <v>26543</v>
       </c>
@@ -12971,7 +12987,7 @@
       </c>
       <c r="H298" s="10"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299" s="7">
         <v>26573</v>
       </c>
@@ -12992,7 +13008,7 @@
       </c>
       <c r="H299" s="10"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300" s="7">
         <v>26604</v>
       </c>
@@ -13013,7 +13029,7 @@
       </c>
       <c r="H300" s="10"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301" s="7">
         <v>26634</v>
       </c>
@@ -13034,7 +13050,7 @@
       </c>
       <c r="H301" s="10"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302" s="7">
         <v>26665</v>
       </c>
@@ -13055,7 +13071,7 @@
       </c>
       <c r="H302" s="10"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A303" s="7">
         <v>26696</v>
       </c>
@@ -13076,7 +13092,7 @@
       </c>
       <c r="H303" s="10"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A304" s="7">
         <v>26724</v>
       </c>
@@ -13097,7 +13113,7 @@
       </c>
       <c r="H304" s="10"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A305" s="7">
         <v>26755</v>
       </c>
@@ -13118,7 +13134,7 @@
       </c>
       <c r="H305" s="10"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306" s="7">
         <v>26785</v>
       </c>
@@ -13139,7 +13155,7 @@
       </c>
       <c r="H306" s="10"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A307" s="7">
         <v>26816</v>
       </c>
@@ -13160,7 +13176,7 @@
       </c>
       <c r="H307" s="10"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A308" s="7">
         <v>26846</v>
       </c>
@@ -13181,7 +13197,7 @@
       </c>
       <c r="H308" s="10"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A309" s="7">
         <v>26877</v>
       </c>
@@ -13202,7 +13218,7 @@
       </c>
       <c r="H309" s="10"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310" s="7">
         <v>26908</v>
       </c>
@@ -13223,7 +13239,7 @@
       </c>
       <c r="H310" s="10"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311" s="7">
         <v>26938</v>
       </c>
@@ -13244,7 +13260,7 @@
       </c>
       <c r="H311" s="10"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A312" s="7">
         <v>26969</v>
       </c>
@@ -13265,7 +13281,7 @@
       </c>
       <c r="H312" s="10"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313" s="7">
         <v>26999</v>
       </c>
@@ -13286,7 +13302,7 @@
       </c>
       <c r="H313" s="10"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A314" s="7">
         <v>27030</v>
       </c>
@@ -13307,7 +13323,7 @@
       </c>
       <c r="H314" s="10"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A315" s="7">
         <v>27061</v>
       </c>
@@ -13328,7 +13344,7 @@
       </c>
       <c r="H315" s="10"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316" s="7">
         <v>27089</v>
       </c>
@@ -13349,7 +13365,7 @@
       </c>
       <c r="H316" s="10"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317" s="7">
         <v>27120</v>
       </c>
@@ -13370,7 +13386,7 @@
       </c>
       <c r="H317" s="10"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318" s="7">
         <v>27150</v>
       </c>
@@ -13391,7 +13407,7 @@
       </c>
       <c r="H318" s="10"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A319" s="7">
         <v>27181</v>
       </c>
@@ -13412,7 +13428,7 @@
       </c>
       <c r="H319" s="10"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A320" s="7">
         <v>27211</v>
       </c>
@@ -13433,7 +13449,7 @@
       </c>
       <c r="H320" s="10"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321" s="7">
         <v>27242</v>
       </c>
@@ -13454,7 +13470,7 @@
       </c>
       <c r="H321" s="10"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322" s="7">
         <v>27273</v>
       </c>
@@ -13475,7 +13491,7 @@
       </c>
       <c r="H322" s="10"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A323" s="7">
         <v>27303</v>
       </c>
@@ -13496,7 +13512,7 @@
       </c>
       <c r="H323" s="10"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A324" s="7">
         <v>27334</v>
       </c>
@@ -13517,7 +13533,7 @@
       </c>
       <c r="H324" s="10"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325" s="7">
         <v>27364</v>
       </c>
@@ -13538,7 +13554,7 @@
       </c>
       <c r="H325" s="10"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" s="7">
         <v>27395</v>
       </c>
@@ -13559,7 +13575,7 @@
       </c>
       <c r="H326" s="10"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A327" s="7">
         <v>27426</v>
       </c>
@@ -13580,7 +13596,7 @@
       </c>
       <c r="H327" s="10"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328" s="7">
         <v>27454</v>
       </c>
@@ -13601,7 +13617,7 @@
       </c>
       <c r="H328" s="10"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" s="7">
         <v>27485</v>
       </c>
@@ -13622,7 +13638,7 @@
       </c>
       <c r="H329" s="10"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" s="7">
         <v>27515</v>
       </c>
@@ -13643,7 +13659,7 @@
       </c>
       <c r="H330" s="10"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" s="7">
         <v>27546</v>
       </c>
@@ -13664,7 +13680,7 @@
       </c>
       <c r="H331" s="10"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" s="7">
         <v>27576</v>
       </c>
@@ -13685,7 +13701,7 @@
       </c>
       <c r="H332" s="10"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A333" s="7">
         <v>27607</v>
       </c>
@@ -13706,7 +13722,7 @@
       </c>
       <c r="H333" s="10"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" s="7">
         <v>27638</v>
       </c>
@@ -13727,7 +13743,7 @@
       </c>
       <c r="H334" s="10"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A335" s="7">
         <v>27668</v>
       </c>
@@ -13748,7 +13764,7 @@
       </c>
       <c r="H335" s="10"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336" s="7">
         <v>27699</v>
       </c>
@@ -13769,7 +13785,7 @@
       </c>
       <c r="H336" s="10"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A337" s="7">
         <v>27729</v>
       </c>
@@ -13790,7 +13806,7 @@
       </c>
       <c r="H337" s="10"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A338" s="7">
         <v>27760</v>
       </c>
@@ -13811,7 +13827,7 @@
       </c>
       <c r="H338" s="10"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A339" s="7">
         <v>27791</v>
       </c>
@@ -13832,7 +13848,7 @@
       </c>
       <c r="H339" s="10"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A340" s="7">
         <v>27820</v>
       </c>
@@ -13853,7 +13869,7 @@
       </c>
       <c r="H340" s="10"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A341" s="7">
         <v>27851</v>
       </c>
@@ -13874,7 +13890,7 @@
       </c>
       <c r="H341" s="10"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A342" s="7">
         <v>27881</v>
       </c>
@@ -13895,7 +13911,7 @@
       </c>
       <c r="H342" s="10"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A343" s="7">
         <v>27912</v>
       </c>
@@ -13916,7 +13932,7 @@
       </c>
       <c r="H343" s="10"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344" s="7">
         <v>27942</v>
       </c>
@@ -13937,7 +13953,7 @@
       </c>
       <c r="H344" s="10"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345" s="7">
         <v>27973</v>
       </c>
@@ -13958,7 +13974,7 @@
       </c>
       <c r="H345" s="10"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A346" s="7">
         <v>28004</v>
       </c>
@@ -13979,7 +13995,7 @@
       </c>
       <c r="H346" s="10"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A347" s="7">
         <v>28034</v>
       </c>
@@ -14000,7 +14016,7 @@
       </c>
       <c r="H347" s="10"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A348" s="7">
         <v>28065</v>
       </c>
@@ -14021,7 +14037,7 @@
       </c>
       <c r="H348" s="10"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A349" s="7">
         <v>28095</v>
       </c>
@@ -14042,7 +14058,7 @@
       </c>
       <c r="H349" s="10"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A350" s="7">
         <v>28126</v>
       </c>
@@ -14063,7 +14079,7 @@
       </c>
       <c r="H350" s="10"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A351" s="7">
         <v>28157</v>
       </c>
@@ -14084,7 +14100,7 @@
       </c>
       <c r="H351" s="10"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A352" s="7">
         <v>28185</v>
       </c>
@@ -14105,7 +14121,7 @@
       </c>
       <c r="H352" s="10"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A353" s="7">
         <v>28216</v>
       </c>
@@ -14126,7 +14142,7 @@
       </c>
       <c r="H353" s="10"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A354" s="7">
         <v>28246</v>
       </c>
@@ -14147,7 +14163,7 @@
       </c>
       <c r="H354" s="10"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A355" s="7">
         <v>28277</v>
       </c>
@@ -14168,7 +14184,7 @@
       </c>
       <c r="H355" s="10"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A356" s="7">
         <v>28307</v>
       </c>
@@ -14189,7 +14205,7 @@
       </c>
       <c r="H356" s="10"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A357" s="7">
         <v>28338</v>
       </c>
@@ -14210,7 +14226,7 @@
       </c>
       <c r="H357" s="10"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A358" s="7">
         <v>28369</v>
       </c>
@@ -14231,7 +14247,7 @@
       </c>
       <c r="H358" s="10"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A359" s="7">
         <v>28399</v>
       </c>
@@ -14252,7 +14268,7 @@
       </c>
       <c r="H359" s="10"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A360" s="7">
         <v>28430</v>
       </c>
@@ -14273,7 +14289,7 @@
       </c>
       <c r="H360" s="10"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A361" s="7">
         <v>28460</v>
       </c>
@@ -14294,7 +14310,7 @@
       </c>
       <c r="H361" s="10"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A362" s="7">
         <v>28491</v>
       </c>
@@ -14315,7 +14331,7 @@
       </c>
       <c r="H362" s="10"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A363" s="7">
         <v>28522</v>
       </c>
@@ -14336,7 +14352,7 @@
       </c>
       <c r="H363" s="10"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A364" s="7">
         <v>28550</v>
       </c>
@@ -14357,7 +14373,7 @@
       </c>
       <c r="H364" s="10"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A365" s="7">
         <v>28581</v>
       </c>
@@ -14378,7 +14394,7 @@
       </c>
       <c r="H365" s="10"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A366" s="7">
         <v>28611</v>
       </c>
@@ -14399,7 +14415,7 @@
       </c>
       <c r="H366" s="10"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A367" s="7">
         <v>28642</v>
       </c>
@@ -14420,7 +14436,7 @@
       </c>
       <c r="H367" s="10"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A368" s="7">
         <v>28672</v>
       </c>
@@ -14441,7 +14457,7 @@
       </c>
       <c r="H368" s="10"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A369" s="7">
         <v>28703</v>
       </c>
@@ -14462,7 +14478,7 @@
       </c>
       <c r="H369" s="10"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A370" s="7">
         <v>28734</v>
       </c>
@@ -14483,7 +14499,7 @@
       </c>
       <c r="H370" s="10"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A371" s="7">
         <v>28764</v>
       </c>
@@ -14504,7 +14520,7 @@
       </c>
       <c r="H371" s="10"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A372" s="7">
         <v>28795</v>
       </c>
@@ -14525,7 +14541,7 @@
       </c>
       <c r="H372" s="10"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A373" s="7">
         <v>28825</v>
       </c>
@@ -14546,7 +14562,7 @@
       </c>
       <c r="H373" s="10"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A374" s="7">
         <v>28856</v>
       </c>
@@ -14567,7 +14583,7 @@
       </c>
       <c r="H374" s="10"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A375" s="7">
         <v>28887</v>
       </c>
@@ -14588,7 +14604,7 @@
       </c>
       <c r="H375" s="10"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A376" s="7">
         <v>28915</v>
       </c>
@@ -14609,7 +14625,7 @@
       </c>
       <c r="H376" s="10"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A377" s="7">
         <v>28946</v>
       </c>
@@ -14630,7 +14646,7 @@
       </c>
       <c r="H377" s="10"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A378" s="7">
         <v>28976</v>
       </c>
@@ -14651,7 +14667,7 @@
       </c>
       <c r="H378" s="10"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A379" s="7">
         <v>29007</v>
       </c>
@@ -14672,7 +14688,7 @@
       </c>
       <c r="H379" s="10"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A380" s="7">
         <v>29037</v>
       </c>
@@ -14693,7 +14709,7 @@
       </c>
       <c r="H380" s="10"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A381" s="7">
         <v>29068</v>
       </c>
@@ -14714,7 +14730,7 @@
       </c>
       <c r="H381" s="10"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A382" s="7">
         <v>29099</v>
       </c>
@@ -14735,7 +14751,7 @@
       </c>
       <c r="H382" s="10"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A383" s="7">
         <v>29129</v>
       </c>
@@ -14756,7 +14772,7 @@
       </c>
       <c r="H383" s="10"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A384" s="7">
         <v>29160</v>
       </c>
@@ -14777,7 +14793,7 @@
       </c>
       <c r="H384" s="10"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A385" s="7">
         <v>29190</v>
       </c>
@@ -14798,7 +14814,7 @@
       </c>
       <c r="H385" s="10"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A386" s="7">
         <v>29221</v>
       </c>
@@ -14819,7 +14835,7 @@
       </c>
       <c r="H386" s="10"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A387" s="7">
         <v>29252</v>
       </c>
@@ -14840,7 +14856,7 @@
       </c>
       <c r="H387" s="10"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A388" s="7">
         <v>29281</v>
       </c>
@@ -14861,7 +14877,7 @@
       </c>
       <c r="H388" s="10"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A389" s="7">
         <v>29312</v>
       </c>
@@ -14882,7 +14898,7 @@
       </c>
       <c r="H389" s="10"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A390" s="7">
         <v>29342</v>
       </c>
@@ -14903,7 +14919,7 @@
       </c>
       <c r="H390" s="10"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A391" s="7">
         <v>29373</v>
       </c>
@@ -14924,7 +14940,7 @@
       </c>
       <c r="H391" s="10"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A392" s="7">
         <v>29403</v>
       </c>
@@ -14945,7 +14961,7 @@
       </c>
       <c r="H392" s="10"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A393" s="7">
         <v>29434</v>
       </c>
@@ -14966,7 +14982,7 @@
       </c>
       <c r="H393" s="10"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A394" s="7">
         <v>29465</v>
       </c>
@@ -14987,7 +15003,7 @@
       </c>
       <c r="H394" s="10"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A395" s="7">
         <v>29495</v>
       </c>
@@ -15008,7 +15024,7 @@
       </c>
       <c r="H395" s="10"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A396" s="7">
         <v>29526</v>
       </c>
@@ -15029,7 +15045,7 @@
       </c>
       <c r="H396" s="10"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A397" s="7">
         <v>29556</v>
       </c>
@@ -15050,7 +15066,7 @@
       </c>
       <c r="H397" s="10"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A398" s="7">
         <v>29587</v>
       </c>
@@ -15071,7 +15087,7 @@
       </c>
       <c r="H398" s="10"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A399" s="7">
         <v>29618</v>
       </c>
@@ -15092,7 +15108,7 @@
       </c>
       <c r="H399" s="10"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A400" s="7">
         <v>29646</v>
       </c>
@@ -15113,7 +15129,7 @@
       </c>
       <c r="H400" s="10"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A401" s="7">
         <v>29677</v>
       </c>
@@ -15134,7 +15150,7 @@
       </c>
       <c r="H401" s="10"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A402" s="7">
         <v>29707</v>
       </c>
@@ -15155,7 +15171,7 @@
       </c>
       <c r="H402" s="10"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A403" s="7">
         <v>29738</v>
       </c>
@@ -15176,7 +15192,7 @@
       </c>
       <c r="H403" s="10"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A404" s="7">
         <v>29768</v>
       </c>
@@ -15197,7 +15213,7 @@
       </c>
       <c r="H404" s="10"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A405" s="7">
         <v>29799</v>
       </c>
@@ -15218,7 +15234,7 @@
       </c>
       <c r="H405" s="10"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A406" s="7">
         <v>29830</v>
       </c>
@@ -15239,7 +15255,7 @@
       </c>
       <c r="H406" s="10"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A407" s="7">
         <v>29860</v>
       </c>
@@ -15260,7 +15276,7 @@
       </c>
       <c r="H407" s="10"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A408" s="7">
         <v>29891</v>
       </c>
@@ -15281,7 +15297,7 @@
       </c>
       <c r="H408" s="10"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A409" s="7">
         <v>29921</v>
       </c>
@@ -15302,7 +15318,7 @@
       </c>
       <c r="H409" s="10"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A410" s="7">
         <v>29952</v>
       </c>
@@ -15323,7 +15339,7 @@
       </c>
       <c r="H410" s="10"/>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A411" s="7">
         <v>29983</v>
       </c>
@@ -15344,7 +15360,7 @@
       </c>
       <c r="H411" s="10"/>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A412" s="7">
         <v>30011</v>
       </c>
@@ -15365,7 +15381,7 @@
       </c>
       <c r="H412" s="10"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A413" s="7">
         <v>30042</v>
       </c>
@@ -15386,7 +15402,7 @@
       </c>
       <c r="H413" s="10"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A414" s="7">
         <v>30072</v>
       </c>
@@ -15407,7 +15423,7 @@
       </c>
       <c r="H414" s="10"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A415" s="7">
         <v>30103</v>
       </c>
@@ -15428,7 +15444,7 @@
       </c>
       <c r="H415" s="10"/>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A416" s="7">
         <v>30133</v>
       </c>
@@ -15449,7 +15465,7 @@
       </c>
       <c r="H416" s="10"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A417" s="7">
         <v>30164</v>
       </c>
@@ -15470,7 +15486,7 @@
       </c>
       <c r="H417" s="10"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A418" s="7">
         <v>30195</v>
       </c>
@@ -15491,7 +15507,7 @@
       </c>
       <c r="H418" s="10"/>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A419" s="7">
         <v>30225</v>
       </c>
@@ -15512,7 +15528,7 @@
       </c>
       <c r="H419" s="10"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A420" s="7">
         <v>30256</v>
       </c>
@@ -15533,7 +15549,7 @@
       </c>
       <c r="H420" s="10"/>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A421" s="7">
         <v>30286</v>
       </c>
@@ -15554,7 +15570,7 @@
       </c>
       <c r="H421" s="10"/>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A422" s="7">
         <v>30317</v>
       </c>
@@ -15575,7 +15591,7 @@
       </c>
       <c r="H422" s="10"/>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A423" s="7">
         <v>30348</v>
       </c>
@@ -15596,7 +15612,7 @@
       </c>
       <c r="H423" s="10"/>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A424" s="7">
         <v>30376</v>
       </c>
@@ -15617,7 +15633,7 @@
       </c>
       <c r="H424" s="10"/>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A425" s="7">
         <v>30407</v>
       </c>
@@ -15638,7 +15654,7 @@
       </c>
       <c r="H425" s="10"/>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A426" s="7">
         <v>30437</v>
       </c>
@@ -15659,7 +15675,7 @@
       </c>
       <c r="H426" s="10"/>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A427" s="7">
         <v>30468</v>
       </c>
@@ -15680,7 +15696,7 @@
       </c>
       <c r="H427" s="10"/>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A428" s="7">
         <v>30498</v>
       </c>
@@ -15701,7 +15717,7 @@
       </c>
       <c r="H428" s="10"/>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A429" s="7">
         <v>30529</v>
       </c>
@@ -15722,7 +15738,7 @@
       </c>
       <c r="H429" s="10"/>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A430" s="7">
         <v>30560</v>
       </c>
@@ -15743,7 +15759,7 @@
       </c>
       <c r="H430" s="10"/>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A431" s="7">
         <v>30590</v>
       </c>
@@ -15764,7 +15780,7 @@
       </c>
       <c r="H431" s="10"/>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A432" s="7">
         <v>30621</v>
       </c>
@@ -15785,7 +15801,7 @@
       </c>
       <c r="H432" s="10"/>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A433" s="7">
         <v>30651</v>
       </c>
@@ -15806,7 +15822,7 @@
       </c>
       <c r="H433" s="10"/>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A434" s="7">
         <v>30682</v>
       </c>
@@ -15827,7 +15843,7 @@
       </c>
       <c r="H434" s="10"/>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A435" s="7">
         <v>30713</v>
       </c>
@@ -15848,7 +15864,7 @@
       </c>
       <c r="H435" s="10"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A436" s="7">
         <v>30742</v>
       </c>
@@ -15869,7 +15885,7 @@
       </c>
       <c r="H436" s="10"/>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A437" s="7">
         <v>30773</v>
       </c>
@@ -15890,7 +15906,7 @@
       </c>
       <c r="H437" s="10"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A438" s="7">
         <v>30803</v>
       </c>
@@ -15911,7 +15927,7 @@
       </c>
       <c r="H438" s="10"/>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A439" s="7">
         <v>30834</v>
       </c>
@@ -15932,7 +15948,7 @@
       </c>
       <c r="H439" s="10"/>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A440" s="7">
         <v>30864</v>
       </c>
@@ -15953,7 +15969,7 @@
       </c>
       <c r="H440" s="10"/>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A441" s="7">
         <v>30895</v>
       </c>
@@ -15974,7 +15990,7 @@
       </c>
       <c r="H441" s="10"/>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A442" s="7">
         <v>30926</v>
       </c>
@@ -15995,7 +16011,7 @@
       </c>
       <c r="H442" s="10"/>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A443" s="7">
         <v>30956</v>
       </c>
@@ -16016,7 +16032,7 @@
       </c>
       <c r="H443" s="10"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A444" s="7">
         <v>30987</v>
       </c>
@@ -16037,7 +16053,7 @@
       </c>
       <c r="H444" s="10"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A445" s="7">
         <v>31017</v>
       </c>
@@ -16058,7 +16074,7 @@
       </c>
       <c r="H445" s="10"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A446" s="7">
         <v>31048</v>
       </c>
@@ -16079,7 +16095,7 @@
       </c>
       <c r="H446" s="10"/>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A447" s="7">
         <v>31079</v>
       </c>
@@ -16100,7 +16116,7 @@
       </c>
       <c r="H447" s="10"/>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A448" s="7">
         <v>31107</v>
       </c>
@@ -16121,7 +16137,7 @@
       </c>
       <c r="H448" s="10"/>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A449" s="7">
         <v>31138</v>
       </c>
@@ -16142,7 +16158,7 @@
       </c>
       <c r="H449" s="10"/>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A450" s="7">
         <v>31168</v>
       </c>
@@ -16163,7 +16179,7 @@
       </c>
       <c r="H450" s="10"/>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A451" s="7">
         <v>31199</v>
       </c>
@@ -16184,7 +16200,7 @@
       </c>
       <c r="H451" s="10"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A452" s="7">
         <v>31229</v>
       </c>
@@ -16205,7 +16221,7 @@
       </c>
       <c r="H452" s="10"/>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A453" s="7">
         <v>31260</v>
       </c>
@@ -16226,7 +16242,7 @@
       </c>
       <c r="H453" s="10"/>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A454" s="7">
         <v>31291</v>
       </c>
@@ -16247,7 +16263,7 @@
       </c>
       <c r="H454" s="10"/>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A455" s="7">
         <v>31321</v>
       </c>
@@ -16268,7 +16284,7 @@
       </c>
       <c r="H455" s="10"/>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A456" s="7">
         <v>31352</v>
       </c>
@@ -16289,7 +16305,7 @@
       </c>
       <c r="H456" s="10"/>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A457" s="7">
         <v>31382</v>
       </c>
@@ -16310,7 +16326,7 @@
       </c>
       <c r="H457" s="10"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A458" s="7">
         <v>31413</v>
       </c>
@@ -16331,7 +16347,7 @@
       </c>
       <c r="H458" s="10"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A459" s="7">
         <v>31444</v>
       </c>
@@ -16352,7 +16368,7 @@
       </c>
       <c r="H459" s="10"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A460" s="7">
         <v>31472</v>
       </c>
@@ -16373,7 +16389,7 @@
       </c>
       <c r="H460" s="10"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A461" s="7">
         <v>31503</v>
       </c>
@@ -16394,7 +16410,7 @@
       </c>
       <c r="H461" s="10"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A462" s="7">
         <v>31533</v>
       </c>
@@ -16415,7 +16431,7 @@
       </c>
       <c r="H462" s="10"/>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A463" s="7">
         <v>31564</v>
       </c>
@@ -16436,7 +16452,7 @@
       </c>
       <c r="H463" s="10"/>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A464" s="7">
         <v>31594</v>
       </c>
@@ -16457,7 +16473,7 @@
       </c>
       <c r="H464" s="10"/>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A465" s="7">
         <v>31625</v>
       </c>
@@ -16478,7 +16494,7 @@
       </c>
       <c r="H465" s="10"/>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A466" s="7">
         <v>31656</v>
       </c>
@@ -16499,7 +16515,7 @@
       </c>
       <c r="H466" s="10"/>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A467" s="7">
         <v>31686</v>
       </c>
@@ -16520,7 +16536,7 @@
       </c>
       <c r="H467" s="10"/>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A468" s="7">
         <v>31717</v>
       </c>
@@ -16541,7 +16557,7 @@
       </c>
       <c r="H468" s="10"/>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A469" s="7">
         <v>31747</v>
       </c>
@@ -16562,7 +16578,7 @@
       </c>
       <c r="H469" s="10"/>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A470" s="7">
         <v>31778</v>
       </c>
@@ -16583,7 +16599,7 @@
       </c>
       <c r="H470" s="10"/>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A471" s="7">
         <v>31809</v>
       </c>
@@ -16604,7 +16620,7 @@
       </c>
       <c r="H471" s="10"/>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A472" s="7">
         <v>31837</v>
       </c>
@@ -16625,7 +16641,7 @@
       </c>
       <c r="H472" s="10"/>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A473" s="7">
         <v>31868</v>
       </c>
@@ -16646,7 +16662,7 @@
       </c>
       <c r="H473" s="10"/>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A474" s="7">
         <v>31898</v>
       </c>
@@ -16667,7 +16683,7 @@
       </c>
       <c r="H474" s="10"/>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A475" s="7">
         <v>31929</v>
       </c>
@@ -16688,7 +16704,7 @@
       </c>
       <c r="H475" s="10"/>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A476" s="7">
         <v>31959</v>
       </c>
@@ -16709,7 +16725,7 @@
       </c>
       <c r="H476" s="10"/>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A477" s="7">
         <v>31990</v>
       </c>
@@ -16730,7 +16746,7 @@
       </c>
       <c r="H477" s="10"/>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A478" s="7">
         <v>32021</v>
       </c>
@@ -16751,7 +16767,7 @@
       </c>
       <c r="H478" s="10"/>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A479" s="7">
         <v>32051</v>
       </c>
@@ -16772,7 +16788,7 @@
       </c>
       <c r="H479" s="10"/>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A480" s="7">
         <v>32082</v>
       </c>
@@ -16793,7 +16809,7 @@
       </c>
       <c r="H480" s="10"/>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A481" s="7">
         <v>32112</v>
       </c>
@@ -16814,7 +16830,7 @@
       </c>
       <c r="H481" s="10"/>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A482" s="7">
         <v>32143</v>
       </c>
@@ -16835,7 +16851,7 @@
       </c>
       <c r="H482" s="10"/>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A483" s="7">
         <v>32174</v>
       </c>
@@ -16856,7 +16872,7 @@
       </c>
       <c r="H483" s="10"/>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A484" s="7">
         <v>32203</v>
       </c>
@@ -16877,7 +16893,7 @@
       </c>
       <c r="H484" s="10"/>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A485" s="7">
         <v>32234</v>
       </c>
@@ -16898,7 +16914,7 @@
       </c>
       <c r="H485" s="10"/>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A486" s="7">
         <v>32264</v>
       </c>
@@ -16919,7 +16935,7 @@
       </c>
       <c r="H486" s="10"/>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A487" s="7">
         <v>32295</v>
       </c>
@@ -16940,7 +16956,7 @@
       </c>
       <c r="H487" s="10"/>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A488" s="7">
         <v>32325</v>
       </c>
@@ -16961,7 +16977,7 @@
       </c>
       <c r="H488" s="10"/>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A489" s="7">
         <v>32356</v>
       </c>
@@ -16982,7 +16998,7 @@
       </c>
       <c r="H489" s="10"/>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A490" s="7">
         <v>32387</v>
       </c>
@@ -17003,7 +17019,7 @@
       </c>
       <c r="H490" s="10"/>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A491" s="7">
         <v>32417</v>
       </c>
@@ -17024,7 +17040,7 @@
       </c>
       <c r="H491" s="10"/>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A492" s="7">
         <v>32448</v>
       </c>
@@ -17045,7 +17061,7 @@
       </c>
       <c r="H492" s="10"/>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A493" s="7">
         <v>32478</v>
       </c>
@@ -17066,7 +17082,7 @@
       </c>
       <c r="H493" s="10"/>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A494" s="7">
         <v>32509</v>
       </c>
@@ -17087,7 +17103,7 @@
       </c>
       <c r="H494" s="10"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A495" s="7">
         <v>32540</v>
       </c>
@@ -17108,7 +17124,7 @@
       </c>
       <c r="H495" s="10"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A496" s="7">
         <v>32568</v>
       </c>
@@ -17129,7 +17145,7 @@
       </c>
       <c r="H496" s="10"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A497" s="7">
         <v>32599</v>
       </c>
@@ -17150,7 +17166,7 @@
       </c>
       <c r="H497" s="10"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A498" s="7">
         <v>32629</v>
       </c>
@@ -17171,7 +17187,7 @@
       </c>
       <c r="H498" s="10"/>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A499" s="7">
         <v>32660</v>
       </c>
@@ -17192,7 +17208,7 @@
       </c>
       <c r="H499" s="10"/>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A500" s="7">
         <v>32690</v>
       </c>
@@ -17213,7 +17229,7 @@
       </c>
       <c r="H500" s="10"/>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A501" s="7">
         <v>32721</v>
       </c>
@@ -17234,7 +17250,7 @@
       </c>
       <c r="H501" s="10"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A502" s="7">
         <v>32752</v>
       </c>
@@ -17255,7 +17271,7 @@
       </c>
       <c r="H502" s="10"/>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A503" s="7">
         <v>32782</v>
       </c>
@@ -17276,7 +17292,7 @@
       </c>
       <c r="H503" s="10"/>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A504" s="7">
         <v>32813</v>
       </c>
@@ -17297,7 +17313,7 @@
       </c>
       <c r="H504" s="10"/>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A505" s="7">
         <v>32843</v>
       </c>
@@ -17318,7 +17334,7 @@
       </c>
       <c r="H505" s="10"/>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A506" s="7">
         <v>32874</v>
       </c>
@@ -17339,7 +17355,7 @@
       </c>
       <c r="H506" s="10"/>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A507" s="7">
         <v>32905</v>
       </c>
@@ -17360,7 +17376,7 @@
       </c>
       <c r="H507" s="10"/>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A508" s="7">
         <v>32933</v>
       </c>
@@ -17381,7 +17397,7 @@
       </c>
       <c r="H508" s="10"/>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A509" s="7">
         <v>32964</v>
       </c>
@@ -17402,7 +17418,7 @@
       </c>
       <c r="H509" s="10"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A510" s="7">
         <v>32994</v>
       </c>
@@ -17423,7 +17439,7 @@
       </c>
       <c r="H510" s="10"/>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A511" s="7">
         <v>33025</v>
       </c>
@@ -17444,7 +17460,7 @@
       </c>
       <c r="H511" s="10"/>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A512" s="7">
         <v>33055</v>
       </c>
@@ -17465,7 +17481,7 @@
       </c>
       <c r="H512" s="10"/>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A513" s="7">
         <v>33086</v>
       </c>
@@ -17486,7 +17502,7 @@
       </c>
       <c r="H513" s="10"/>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A514" s="7">
         <v>33117</v>
       </c>
@@ -17507,7 +17523,7 @@
       </c>
       <c r="H514" s="10"/>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A515" s="7">
         <v>33147</v>
       </c>
@@ -17528,7 +17544,7 @@
       </c>
       <c r="H515" s="10"/>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A516" s="7">
         <v>33178</v>
       </c>
@@ -17549,7 +17565,7 @@
       </c>
       <c r="H516" s="10"/>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A517" s="7">
         <v>33208</v>
       </c>
@@ -17570,7 +17586,7 @@
       </c>
       <c r="H517" s="10"/>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A518" s="7">
         <v>33239</v>
       </c>
@@ -17591,7 +17607,7 @@
       </c>
       <c r="H518" s="10"/>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A519" s="7">
         <v>33270</v>
       </c>
@@ -17612,7 +17628,7 @@
       </c>
       <c r="H519" s="10"/>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A520" s="7">
         <v>33298</v>
       </c>
@@ -17633,7 +17649,7 @@
       </c>
       <c r="H520" s="10"/>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A521" s="7">
         <v>33329</v>
       </c>
@@ -17654,7 +17670,7 @@
       </c>
       <c r="H521" s="10"/>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A522" s="7">
         <v>33359</v>
       </c>
@@ -17675,7 +17691,7 @@
       </c>
       <c r="H522" s="10"/>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A523" s="7">
         <v>33390</v>
       </c>
@@ -17696,7 +17712,7 @@
       </c>
       <c r="H523" s="10"/>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A524" s="7">
         <v>33420</v>
       </c>
@@ -17717,7 +17733,7 @@
       </c>
       <c r="H524" s="10"/>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A525" s="7">
         <v>33451</v>
       </c>
@@ -17738,7 +17754,7 @@
       </c>
       <c r="H525" s="10"/>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A526" s="7">
         <v>33482</v>
       </c>
@@ -17759,7 +17775,7 @@
       </c>
       <c r="H526" s="10"/>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A527" s="7">
         <v>33512</v>
       </c>
@@ -17780,7 +17796,7 @@
       </c>
       <c r="H527" s="10"/>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A528" s="7">
         <v>33543</v>
       </c>
@@ -17801,7 +17817,7 @@
       </c>
       <c r="H528" s="10"/>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A529" s="7">
         <v>33573</v>
       </c>
@@ -17822,7 +17838,7 @@
       </c>
       <c r="H529" s="10"/>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A530" s="7">
         <v>33604</v>
       </c>
@@ -17843,7 +17859,7 @@
       </c>
       <c r="H530" s="10"/>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A531" s="7">
         <v>33635</v>
       </c>
@@ -17864,7 +17880,7 @@
       </c>
       <c r="H531" s="10"/>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A532" s="7">
         <v>33664</v>
       </c>
@@ -17885,7 +17901,7 @@
       </c>
       <c r="H532" s="10"/>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A533" s="7">
         <v>33695</v>
       </c>
@@ -17906,7 +17922,7 @@
       </c>
       <c r="H533" s="10"/>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" s="7">
         <v>33725</v>
       </c>
@@ -17927,7 +17943,7 @@
       </c>
       <c r="H534" s="10"/>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A535" s="7">
         <v>33756</v>
       </c>
@@ -17948,7 +17964,7 @@
       </c>
       <c r="H535" s="10"/>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" s="7">
         <v>33786</v>
       </c>
@@ -17969,7 +17985,7 @@
       </c>
       <c r="H536" s="10"/>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A537" s="7">
         <v>33817</v>
       </c>
@@ -17990,7 +18006,7 @@
       </c>
       <c r="H537" s="10"/>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A538" s="7">
         <v>33848</v>
       </c>
@@ -18011,7 +18027,7 @@
       </c>
       <c r="H538" s="10"/>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A539" s="7">
         <v>33878</v>
       </c>
@@ -18032,7 +18048,7 @@
       </c>
       <c r="H539" s="10"/>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A540" s="7">
         <v>33909</v>
       </c>
@@ -18053,7 +18069,7 @@
       </c>
       <c r="H540" s="10"/>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A541" s="7">
         <v>33939</v>
       </c>
@@ -18074,7 +18090,7 @@
       </c>
       <c r="H541" s="10"/>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A542" s="7">
         <v>33970</v>
       </c>
@@ -18095,7 +18111,7 @@
       </c>
       <c r="H542" s="10"/>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A543" s="7">
         <v>34001</v>
       </c>
@@ -18116,7 +18132,7 @@
       </c>
       <c r="H543" s="10"/>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A544" s="7">
         <v>34029</v>
       </c>
@@ -18137,7 +18153,7 @@
       </c>
       <c r="H544" s="10"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A545" s="7">
         <v>34060</v>
       </c>
@@ -18158,7 +18174,7 @@
       </c>
       <c r="H545" s="10"/>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A546" s="7">
         <v>34090</v>
       </c>
@@ -18179,7 +18195,7 @@
       </c>
       <c r="H546" s="10"/>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A547" s="7">
         <v>34121</v>
       </c>
@@ -18200,7 +18216,7 @@
       </c>
       <c r="H547" s="10"/>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A548" s="7">
         <v>34151</v>
       </c>
@@ -18221,7 +18237,7 @@
       </c>
       <c r="H548" s="10"/>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A549" s="7">
         <v>34182</v>
       </c>
@@ -18242,7 +18258,7 @@
       </c>
       <c r="H549" s="10"/>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A550" s="7">
         <v>34213</v>
       </c>
@@ -18263,7 +18279,7 @@
       </c>
       <c r="H550" s="10"/>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A551" s="7">
         <v>34243</v>
       </c>
@@ -18284,7 +18300,7 @@
       </c>
       <c r="H551" s="10"/>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A552" s="7">
         <v>34274</v>
       </c>
@@ -18305,7 +18321,7 @@
       </c>
       <c r="H552" s="10"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A553" s="7">
         <v>34304</v>
       </c>
@@ -18326,7 +18342,7 @@
       </c>
       <c r="H553" s="10"/>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A554" s="7">
         <v>34335</v>
       </c>
@@ -18347,7 +18363,7 @@
       </c>
       <c r="H554" s="10"/>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A555" s="7">
         <v>34366</v>
       </c>
@@ -18368,7 +18384,7 @@
       </c>
       <c r="H555" s="10"/>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A556" s="7">
         <v>34394</v>
       </c>
@@ -18389,7 +18405,7 @@
       </c>
       <c r="H556" s="10"/>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A557" s="7">
         <v>34425</v>
       </c>
@@ -18410,7 +18426,7 @@
       </c>
       <c r="H557" s="10"/>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A558" s="7">
         <v>34455</v>
       </c>
@@ -18431,7 +18447,7 @@
       </c>
       <c r="H558" s="10"/>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A559" s="7">
         <v>34486</v>
       </c>
@@ -18452,7 +18468,7 @@
       </c>
       <c r="H559" s="10"/>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A560" s="7">
         <v>34516</v>
       </c>
@@ -18473,7 +18489,7 @@
       </c>
       <c r="H560" s="10"/>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A561" s="7">
         <v>34547</v>
       </c>
@@ -18494,7 +18510,7 @@
       </c>
       <c r="H561" s="10"/>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A562" s="7">
         <v>34578</v>
       </c>
@@ -18515,7 +18531,7 @@
       </c>
       <c r="H562" s="10"/>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A563" s="7">
         <v>34608</v>
       </c>
@@ -18536,7 +18552,7 @@
       </c>
       <c r="H563" s="10"/>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A564" s="7">
         <v>34639</v>
       </c>
@@ -18557,7 +18573,7 @@
       </c>
       <c r="H564" s="10"/>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A565" s="7">
         <v>34669</v>
       </c>
@@ -18578,7 +18594,7 @@
       </c>
       <c r="H565" s="10"/>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A566" s="7">
         <v>34700</v>
       </c>
@@ -18599,7 +18615,7 @@
       </c>
       <c r="H566" s="10"/>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A567" s="7">
         <v>34731</v>
       </c>
@@ -18620,7 +18636,7 @@
       </c>
       <c r="H567" s="10"/>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A568" s="7">
         <v>34759</v>
       </c>
@@ -18641,7 +18657,7 @@
       </c>
       <c r="H568" s="10"/>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A569" s="7">
         <v>34790</v>
       </c>
@@ -18662,7 +18678,7 @@
       </c>
       <c r="H569" s="10"/>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A570" s="7">
         <v>34820</v>
       </c>
@@ -18683,7 +18699,7 @@
       </c>
       <c r="H570" s="10"/>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A571" s="7">
         <v>34851</v>
       </c>
@@ -18704,7 +18720,7 @@
       </c>
       <c r="H571" s="10"/>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A572" s="7">
         <v>34881</v>
       </c>
@@ -18725,7 +18741,7 @@
       </c>
       <c r="H572" s="10"/>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A573" s="7">
         <v>34912</v>
       </c>
@@ -18746,7 +18762,7 @@
       </c>
       <c r="H573" s="10"/>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A574" s="7">
         <v>34943</v>
       </c>
@@ -18767,7 +18783,7 @@
       </c>
       <c r="H574" s="10"/>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A575" s="7">
         <v>34973</v>
       </c>
@@ -18788,7 +18804,7 @@
       </c>
       <c r="H575" s="10"/>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A576" s="7">
         <v>35004</v>
       </c>
@@ -18809,7 +18825,7 @@
       </c>
       <c r="H576" s="10"/>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A577" s="7">
         <v>35034</v>
       </c>
@@ -18830,7 +18846,7 @@
       </c>
       <c r="H577" s="10"/>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A578" s="7">
         <v>35065</v>
       </c>
@@ -18851,7 +18867,7 @@
       </c>
       <c r="H578" s="10"/>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A579" s="7">
         <v>35096</v>
       </c>
@@ -18872,7 +18888,7 @@
       </c>
       <c r="H579" s="10"/>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A580" s="7">
         <v>35125</v>
       </c>
@@ -18893,7 +18909,7 @@
       </c>
       <c r="H580" s="10"/>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A581" s="7">
         <v>35156</v>
       </c>
@@ -18914,7 +18930,7 @@
       </c>
       <c r="H581" s="10"/>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A582" s="7">
         <v>35186</v>
       </c>
@@ -18935,7 +18951,7 @@
       </c>
       <c r="H582" s="10"/>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A583" s="7">
         <v>35217</v>
       </c>
@@ -18956,7 +18972,7 @@
       </c>
       <c r="H583" s="10"/>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A584" s="7">
         <v>35247</v>
       </c>
@@ -18977,7 +18993,7 @@
       </c>
       <c r="H584" s="10"/>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A585" s="7">
         <v>35278</v>
       </c>
@@ -18998,7 +19014,7 @@
       </c>
       <c r="H585" s="10"/>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A586" s="7">
         <v>35309</v>
       </c>
@@ -19019,7 +19035,7 @@
       </c>
       <c r="H586" s="10"/>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A587" s="7">
         <v>35339</v>
       </c>
@@ -19040,7 +19056,7 @@
       </c>
       <c r="H587" s="10"/>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A588" s="7">
         <v>35370</v>
       </c>
@@ -19061,7 +19077,7 @@
       </c>
       <c r="H588" s="10"/>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A589" s="7">
         <v>35400</v>
       </c>
@@ -19082,7 +19098,7 @@
       </c>
       <c r="H589" s="10"/>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A590" s="7">
         <v>35431</v>
       </c>
@@ -19103,7 +19119,7 @@
       </c>
       <c r="H590" s="10"/>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A591" s="7">
         <v>35462</v>
       </c>
@@ -19124,7 +19140,7 @@
       </c>
       <c r="H591" s="10"/>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A592" s="7">
         <v>35490</v>
       </c>
@@ -19145,7 +19161,7 @@
       </c>
       <c r="H592" s="10"/>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A593" s="7">
         <v>35521</v>
       </c>
@@ -19166,7 +19182,7 @@
       </c>
       <c r="H593" s="10"/>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A594" s="7">
         <v>35551</v>
       </c>
@@ -19187,7 +19203,7 @@
       </c>
       <c r="H594" s="10"/>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A595" s="7">
         <v>35582</v>
       </c>
@@ -19208,7 +19224,7 @@
       </c>
       <c r="H595" s="10"/>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A596" s="7">
         <v>35612</v>
       </c>
@@ -19229,7 +19245,7 @@
       </c>
       <c r="H596" s="10"/>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A597" s="7">
         <v>35643</v>
       </c>
@@ -19250,7 +19266,7 @@
       </c>
       <c r="H597" s="10"/>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A598" s="7">
         <v>35674</v>
       </c>
@@ -19271,7 +19287,7 @@
       </c>
       <c r="H598" s="10"/>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A599" s="7">
         <v>35704</v>
       </c>
@@ -19292,7 +19308,7 @@
       </c>
       <c r="H599" s="10"/>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A600" s="7">
         <v>35735</v>
       </c>
@@ -19313,7 +19329,7 @@
       </c>
       <c r="H600" s="10"/>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A601" s="7">
         <v>35765</v>
       </c>
@@ -19334,7 +19350,7 @@
       </c>
       <c r="H601" s="10"/>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A602" s="7">
         <v>35796</v>
       </c>
@@ -19355,7 +19371,7 @@
       </c>
       <c r="H602" s="10"/>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A603" s="7">
         <v>35827</v>
       </c>
@@ -19376,7 +19392,7 @@
       </c>
       <c r="H603" s="10"/>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A604" s="7">
         <v>35855</v>
       </c>
@@ -19397,7 +19413,7 @@
       </c>
       <c r="H604" s="10"/>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A605" s="7">
         <v>35886</v>
       </c>
@@ -19418,7 +19434,7 @@
       </c>
       <c r="H605" s="10"/>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A606" s="7">
         <v>35916</v>
       </c>
@@ -19439,7 +19455,7 @@
       </c>
       <c r="H606" s="10"/>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A607" s="7">
         <v>35947</v>
       </c>
@@ -19460,7 +19476,7 @@
       </c>
       <c r="H607" s="10"/>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A608" s="7">
         <v>35977</v>
       </c>
@@ -19481,7 +19497,7 @@
       </c>
       <c r="H608" s="10"/>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A609" s="7">
         <v>36008</v>
       </c>
@@ -19502,7 +19518,7 @@
       </c>
       <c r="H609" s="10"/>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A610" s="7">
         <v>36039</v>
       </c>
@@ -19523,7 +19539,7 @@
       </c>
       <c r="H610" s="10"/>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A611" s="7">
         <v>36069</v>
       </c>
@@ -19544,7 +19560,7 @@
       </c>
       <c r="H611" s="10"/>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A612" s="7">
         <v>36100</v>
       </c>
@@ -19565,7 +19581,7 @@
       </c>
       <c r="H612" s="10"/>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A613" s="7">
         <v>36130</v>
       </c>
@@ -19586,7 +19602,7 @@
       </c>
       <c r="H613" s="10"/>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A614" s="7">
         <v>36161</v>
       </c>
@@ -19607,7 +19623,7 @@
       </c>
       <c r="H614" s="10"/>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A615" s="7">
         <v>36192</v>
       </c>
@@ -19628,7 +19644,7 @@
       </c>
       <c r="H615" s="10"/>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A616" s="7">
         <v>36220</v>
       </c>
@@ -19649,7 +19665,7 @@
       </c>
       <c r="H616" s="10"/>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A617" s="7">
         <v>36251</v>
       </c>
@@ -19670,7 +19686,7 @@
       </c>
       <c r="H617" s="10"/>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A618" s="7">
         <v>36281</v>
       </c>
@@ -19691,7 +19707,7 @@
       </c>
       <c r="H618" s="10"/>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A619" s="7">
         <v>36312</v>
       </c>
@@ -19712,7 +19728,7 @@
       </c>
       <c r="H619" s="10"/>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A620" s="7">
         <v>36342</v>
       </c>
@@ -19733,7 +19749,7 @@
       </c>
       <c r="H620" s="10"/>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A621" s="7">
         <v>36373</v>
       </c>
@@ -19754,7 +19770,7 @@
       </c>
       <c r="H621" s="10"/>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A622" s="7">
         <v>36404</v>
       </c>
@@ -19775,7 +19791,7 @@
       </c>
       <c r="H622" s="10"/>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A623" s="7">
         <v>36434</v>
       </c>
@@ -19796,7 +19812,7 @@
       </c>
       <c r="H623" s="10"/>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A624" s="7">
         <v>36465</v>
       </c>
@@ -19817,7 +19833,7 @@
       </c>
       <c r="H624" s="10"/>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A625" s="7">
         <v>36495</v>
       </c>
@@ -19838,7 +19854,7 @@
       </c>
       <c r="H625" s="10"/>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A626" s="7">
         <v>36526</v>
       </c>
@@ -19859,7 +19875,7 @@
       </c>
       <c r="H626" s="10"/>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A627" s="7">
         <v>36557</v>
       </c>
@@ -19880,7 +19896,7 @@
       </c>
       <c r="H627" s="10"/>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A628" s="7">
         <v>36586</v>
       </c>
@@ -19901,7 +19917,7 @@
       </c>
       <c r="H628" s="10"/>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A629" s="7">
         <v>36617</v>
       </c>
@@ -19922,7 +19938,7 @@
       </c>
       <c r="H629" s="10"/>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A630" s="7">
         <v>36647</v>
       </c>
@@ -19943,7 +19959,7 @@
       </c>
       <c r="H630" s="10"/>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A631" s="7">
         <v>36678</v>
       </c>
@@ -19964,7 +19980,7 @@
       </c>
       <c r="H631" s="10"/>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A632" s="7">
         <v>36708</v>
       </c>
@@ -19985,7 +20001,7 @@
       </c>
       <c r="H632" s="10"/>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A633" s="7">
         <v>36739</v>
       </c>
@@ -20006,7 +20022,7 @@
       </c>
       <c r="H633" s="10"/>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A634" s="7">
         <v>36770</v>
       </c>
@@ -20027,7 +20043,7 @@
       </c>
       <c r="H634" s="10"/>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A635" s="7">
         <v>36800</v>
       </c>
@@ -20048,7 +20064,7 @@
       </c>
       <c r="H635" s="10"/>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A636" s="7">
         <v>36831</v>
       </c>
@@ -20069,7 +20085,7 @@
       </c>
       <c r="H636" s="10"/>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A637" s="7">
         <v>36861</v>
       </c>
@@ -20090,7 +20106,7 @@
       </c>
       <c r="H637" s="10"/>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A638" s="7">
         <v>36892</v>
       </c>
@@ -20111,7 +20127,7 @@
       </c>
       <c r="H638" s="10"/>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A639" s="7">
         <v>36923</v>
       </c>
@@ -20132,7 +20148,7 @@
       </c>
       <c r="H639" s="10"/>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A640" s="7">
         <v>36951</v>
       </c>
@@ -20153,7 +20169,7 @@
       </c>
       <c r="H640" s="10"/>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A641" s="7">
         <v>36982</v>
       </c>
@@ -20174,7 +20190,7 @@
       </c>
       <c r="H641" s="10"/>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A642" s="7">
         <v>37012</v>
       </c>
@@ -20195,7 +20211,7 @@
       </c>
       <c r="H642" s="10"/>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A643" s="7">
         <v>37043</v>
       </c>
@@ -20216,7 +20232,7 @@
       </c>
       <c r="H643" s="10"/>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A644" s="7">
         <v>37073</v>
       </c>
@@ -20237,7 +20253,7 @@
       </c>
       <c r="H644" s="10"/>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A645" s="7">
         <v>37104</v>
       </c>
@@ -20258,7 +20274,7 @@
       </c>
       <c r="H645" s="10"/>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A646" s="7">
         <v>37135</v>
       </c>
@@ -20279,7 +20295,7 @@
       </c>
       <c r="H646" s="10"/>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A647" s="7">
         <v>37165</v>
       </c>
@@ -20300,7 +20316,7 @@
       </c>
       <c r="H647" s="10"/>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A648" s="7">
         <v>37196</v>
       </c>
@@ -20321,7 +20337,7 @@
       </c>
       <c r="H648" s="10"/>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A649" s="7">
         <v>37226</v>
       </c>
@@ -20342,7 +20358,7 @@
       </c>
       <c r="H649" s="10"/>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A650" s="7">
         <v>37257</v>
       </c>
@@ -20363,7 +20379,7 @@
       </c>
       <c r="H650" s="10"/>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A651" s="7">
         <v>37288</v>
       </c>
@@ -20384,7 +20400,7 @@
       </c>
       <c r="H651" s="10"/>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A652" s="7">
         <v>37316</v>
       </c>
@@ -20405,7 +20421,7 @@
       </c>
       <c r="H652" s="10"/>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A653" s="7">
         <v>37347</v>
       </c>
@@ -20426,7 +20442,7 @@
       </c>
       <c r="H653" s="10"/>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A654" s="7">
         <v>37377</v>
       </c>
@@ -20447,7 +20463,7 @@
       </c>
       <c r="H654" s="10"/>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A655" s="7">
         <v>37408</v>
       </c>
@@ -20468,7 +20484,7 @@
       </c>
       <c r="H655" s="10"/>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A656" s="7">
         <v>37438</v>
       </c>
@@ -20489,7 +20505,7 @@
       </c>
       <c r="H656" s="10"/>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A657" s="7">
         <v>37469</v>
       </c>
@@ -20510,7 +20526,7 @@
       </c>
       <c r="H657" s="10"/>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A658" s="7">
         <v>37500</v>
       </c>
@@ -20531,7 +20547,7 @@
       </c>
       <c r="H658" s="10"/>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A659" s="7">
         <v>37530</v>
       </c>
@@ -20552,7 +20568,7 @@
       </c>
       <c r="H659" s="10"/>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A660" s="7">
         <v>37561</v>
       </c>
@@ -20573,7 +20589,7 @@
       </c>
       <c r="H660" s="10"/>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A661" s="7">
         <v>37591</v>
       </c>
@@ -20594,7 +20610,7 @@
       </c>
       <c r="H661" s="10"/>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A662" s="7">
         <v>37622</v>
       </c>
@@ -20615,7 +20631,7 @@
       </c>
       <c r="H662" s="10"/>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A663" s="7">
         <v>37653</v>
       </c>
@@ -20636,7 +20652,7 @@
       </c>
       <c r="H663" s="10"/>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A664" s="7">
         <v>37681</v>
       </c>
@@ -20657,7 +20673,7 @@
       </c>
       <c r="H664" s="10"/>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A665" s="7">
         <v>37712</v>
       </c>
@@ -20678,7 +20694,7 @@
       </c>
       <c r="H665" s="10"/>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A666" s="7">
         <v>37742</v>
       </c>
@@ -20699,7 +20715,7 @@
       </c>
       <c r="H666" s="10"/>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A667" s="7">
         <v>37773</v>
       </c>
@@ -20720,7 +20736,7 @@
       </c>
       <c r="H667" s="10"/>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A668" s="7">
         <v>37803</v>
       </c>
@@ -20741,7 +20757,7 @@
       </c>
       <c r="H668" s="10"/>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A669" s="7">
         <v>37834</v>
       </c>
@@ -20762,7 +20778,7 @@
       </c>
       <c r="H669" s="10"/>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A670" s="7">
         <v>37865</v>
       </c>
@@ -20783,7 +20799,7 @@
       </c>
       <c r="H670" s="10"/>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A671" s="7">
         <v>37895</v>
       </c>
@@ -20804,7 +20820,7 @@
       </c>
       <c r="H671" s="10"/>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A672" s="7">
         <v>37926</v>
       </c>
@@ -20825,7 +20841,7 @@
       </c>
       <c r="H672" s="10"/>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A673" s="7">
         <v>37956</v>
       </c>
@@ -20846,7 +20862,7 @@
       </c>
       <c r="H673" s="10"/>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A674" s="7">
         <v>37987</v>
       </c>
@@ -20867,7 +20883,7 @@
       </c>
       <c r="H674" s="10"/>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A675" s="7">
         <v>38018</v>
       </c>
@@ -20888,7 +20904,7 @@
       </c>
       <c r="H675" s="10"/>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A676" s="7">
         <v>38047</v>
       </c>
@@ -20909,7 +20925,7 @@
       </c>
       <c r="H676" s="10"/>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A677" s="7">
         <v>38078</v>
       </c>
@@ -20930,7 +20946,7 @@
       </c>
       <c r="H677" s="10"/>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A678" s="7">
         <v>38108</v>
       </c>
@@ -20951,7 +20967,7 @@
       </c>
       <c r="H678" s="10"/>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A679" s="7">
         <v>38139</v>
       </c>
@@ -20972,7 +20988,7 @@
       </c>
       <c r="H679" s="10"/>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A680" s="7">
         <v>38169</v>
       </c>
@@ -20993,7 +21009,7 @@
       </c>
       <c r="H680" s="10"/>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A681" s="7">
         <v>38200</v>
       </c>
@@ -21014,7 +21030,7 @@
       </c>
       <c r="H681" s="10"/>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A682" s="7">
         <v>38231</v>
       </c>
@@ -21035,7 +21051,7 @@
       </c>
       <c r="H682" s="10"/>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A683" s="7">
         <v>38261</v>
       </c>
@@ -21056,7 +21072,7 @@
       </c>
       <c r="H683" s="10"/>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A684" s="7">
         <v>38292</v>
       </c>
@@ -21077,7 +21093,7 @@
       </c>
       <c r="H684" s="10"/>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A685" s="7">
         <v>38322</v>
       </c>
@@ -21098,7 +21114,7 @@
       </c>
       <c r="H685" s="10"/>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A686" s="7">
         <v>38353</v>
       </c>
@@ -21119,7 +21135,7 @@
       </c>
       <c r="H686" s="10"/>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A687" s="7">
         <v>38384</v>
       </c>
@@ -21140,7 +21156,7 @@
       </c>
       <c r="H687" s="10"/>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A688" s="7">
         <v>38412</v>
       </c>
@@ -21161,7 +21177,7 @@
       </c>
       <c r="H688" s="10"/>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A689" s="7">
         <v>38443</v>
       </c>
@@ -21182,7 +21198,7 @@
       </c>
       <c r="H689" s="10"/>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A690" s="7">
         <v>38473</v>
       </c>
@@ -21203,7 +21219,7 @@
       </c>
       <c r="H690" s="10"/>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A691" s="7">
         <v>38504</v>
       </c>
@@ -21224,7 +21240,7 @@
       </c>
       <c r="H691" s="10"/>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A692" s="7">
         <v>38534</v>
       </c>
@@ -21245,7 +21261,7 @@
       </c>
       <c r="H692" s="10"/>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A693" s="7">
         <v>38565</v>
       </c>
@@ -21266,7 +21282,7 @@
       </c>
       <c r="H693" s="10"/>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A694" s="7">
         <v>38596</v>
       </c>
@@ -21287,7 +21303,7 @@
       </c>
       <c r="H694" s="10"/>
     </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A695" s="7">
         <v>38626</v>
       </c>
@@ -21308,7 +21324,7 @@
       </c>
       <c r="H695" s="10"/>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A696" s="7">
         <v>38657</v>
       </c>
@@ -21329,7 +21345,7 @@
       </c>
       <c r="H696" s="10"/>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A697" s="7">
         <v>38687</v>
       </c>
@@ -21350,7 +21366,7 @@
       </c>
       <c r="H697" s="10"/>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A698" s="7">
         <v>38718</v>
       </c>
@@ -21371,7 +21387,7 @@
       </c>
       <c r="H698" s="10"/>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A699" s="7">
         <v>38749</v>
       </c>
@@ -21392,7 +21408,7 @@
       </c>
       <c r="H699" s="10"/>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A700" s="7">
         <v>38777</v>
       </c>
@@ -21413,7 +21429,7 @@
       </c>
       <c r="H700" s="10"/>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A701" s="7">
         <v>38808</v>
       </c>
@@ -21434,7 +21450,7 @@
       </c>
       <c r="H701" s="10"/>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A702" s="7">
         <v>38838</v>
       </c>
@@ -21455,7 +21471,7 @@
       </c>
       <c r="H702" s="10"/>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A703" s="7">
         <v>38869</v>
       </c>
@@ -21476,7 +21492,7 @@
       </c>
       <c r="H703" s="10"/>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A704" s="7">
         <v>38899</v>
       </c>
@@ -21497,7 +21513,7 @@
       </c>
       <c r="H704" s="10"/>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A705" s="7">
         <v>38930</v>
       </c>
@@ -21518,7 +21534,7 @@
       </c>
       <c r="H705" s="10"/>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A706" s="7">
         <v>38961</v>
       </c>
@@ -21539,7 +21555,7 @@
       </c>
       <c r="H706" s="10"/>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A707" s="7">
         <v>38991</v>
       </c>
@@ -21560,7 +21576,7 @@
       </c>
       <c r="H707" s="10"/>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A708" s="7">
         <v>39022</v>
       </c>
@@ -21581,7 +21597,7 @@
       </c>
       <c r="H708" s="10"/>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A709" s="7">
         <v>39052</v>
       </c>
@@ -21602,7 +21618,7 @@
       </c>
       <c r="H709" s="10"/>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A710" s="7">
         <v>39083</v>
       </c>
@@ -21623,7 +21639,7 @@
       </c>
       <c r="H710" s="10"/>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A711" s="7">
         <v>39114</v>
       </c>
@@ -21644,7 +21660,7 @@
       </c>
       <c r="H711" s="10"/>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A712" s="7">
         <v>39142</v>
       </c>
@@ -21665,7 +21681,7 @@
       </c>
       <c r="H712" s="10"/>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A713" s="7">
         <v>39173</v>
       </c>
@@ -21686,7 +21702,7 @@
       </c>
       <c r="H713" s="10"/>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A714" s="7">
         <v>39203</v>
       </c>
@@ -21707,7 +21723,7 @@
       </c>
       <c r="H714" s="10"/>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A715" s="7">
         <v>39234</v>
       </c>
@@ -21728,7 +21744,7 @@
       </c>
       <c r="H715" s="10"/>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A716" s="7">
         <v>39264</v>
       </c>
@@ -21749,7 +21765,7 @@
       </c>
       <c r="H716" s="10"/>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A717" s="7">
         <v>39295</v>
       </c>
@@ -21770,7 +21786,7 @@
       </c>
       <c r="H717" s="10"/>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A718" s="7">
         <v>39326</v>
       </c>
@@ -21791,7 +21807,7 @@
       </c>
       <c r="H718" s="10"/>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A719" s="7">
         <v>39356</v>
       </c>
@@ -21812,7 +21828,7 @@
       </c>
       <c r="H719" s="10"/>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A720" s="7">
         <v>39387</v>
       </c>
@@ -21833,7 +21849,7 @@
       </c>
       <c r="H720" s="10"/>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A721" s="7">
         <v>39417</v>
       </c>
@@ -21854,7 +21870,7 @@
       </c>
       <c r="H721" s="10"/>
     </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A722" s="7">
         <v>39448</v>
       </c>
@@ -21875,7 +21891,7 @@
       </c>
       <c r="H722" s="10"/>
     </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A723" s="7">
         <v>39479</v>
       </c>
@@ -21896,7 +21912,7 @@
       </c>
       <c r="H723" s="10"/>
     </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A724" s="7">
         <v>39508</v>
       </c>
@@ -21917,7 +21933,7 @@
       </c>
       <c r="H724" s="10"/>
     </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A725" s="7">
         <v>39539</v>
       </c>
@@ -21938,7 +21954,7 @@
       </c>
       <c r="H725" s="10"/>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A726" s="7">
         <v>39569</v>
       </c>
@@ -21959,7 +21975,7 @@
       </c>
       <c r="H726" s="10"/>
     </row>
-    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A727" s="7">
         <v>39600</v>
       </c>
@@ -21980,7 +21996,7 @@
       </c>
       <c r="H727" s="10"/>
     </row>
-    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A728" s="7">
         <v>39630</v>
       </c>
@@ -22004,7 +22020,7 @@
       </c>
       <c r="H728" s="10"/>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A729" s="7">
         <v>39661</v>
       </c>
@@ -22028,7 +22044,7 @@
       </c>
       <c r="H729" s="10"/>
     </row>
-    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A730" s="7">
         <v>39692</v>
       </c>
@@ -22052,7 +22068,7 @@
       </c>
       <c r="H730" s="10"/>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A731" s="7">
         <v>39722</v>
       </c>
@@ -22076,7 +22092,7 @@
       </c>
       <c r="H731" s="10"/>
     </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A732" s="7">
         <v>39753</v>
       </c>
@@ -22100,7 +22116,7 @@
       </c>
       <c r="H732" s="10"/>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A733" s="7">
         <v>39783</v>
       </c>
@@ -22124,7 +22140,7 @@
       </c>
       <c r="H733" s="10"/>
     </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A734" s="7">
         <v>39814</v>
       </c>
@@ -22148,7 +22164,7 @@
       </c>
       <c r="H734" s="10"/>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A735" s="7">
         <v>39845</v>
       </c>
@@ -22172,7 +22188,7 @@
       </c>
       <c r="H735" s="10"/>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A736" s="7">
         <v>39873</v>
       </c>
@@ -22196,7 +22212,7 @@
       </c>
       <c r="H736" s="10"/>
     </row>
-    <row r="737" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A737" s="7">
         <v>39904</v>
       </c>
@@ -22220,7 +22236,7 @@
       </c>
       <c r="H737" s="10"/>
     </row>
-    <row r="738" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A738" s="7">
         <v>39934</v>
       </c>
@@ -22244,7 +22260,7 @@
       </c>
       <c r="H738" s="10"/>
     </row>
-    <row r="739" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A739" s="7">
         <v>39965</v>
       </c>
@@ -22268,7 +22284,7 @@
       </c>
       <c r="H739" s="10"/>
     </row>
-    <row r="740" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A740" s="7">
         <v>39995</v>
       </c>
@@ -22292,7 +22308,7 @@
       </c>
       <c r="H740" s="10"/>
     </row>
-    <row r="741" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A741" s="7">
         <v>40026</v>
       </c>
@@ -22316,7 +22332,7 @@
       </c>
       <c r="H741" s="10"/>
     </row>
-    <row r="742" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A742" s="7">
         <v>40057</v>
       </c>
@@ -22340,7 +22356,7 @@
       </c>
       <c r="H742" s="10"/>
     </row>
-    <row r="743" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A743" s="7">
         <v>40087</v>
       </c>
@@ -22364,7 +22380,7 @@
       </c>
       <c r="H743" s="10"/>
     </row>
-    <row r="744" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A744" s="7">
         <v>40118</v>
       </c>
@@ -22388,7 +22404,7 @@
       </c>
       <c r="H744" s="10"/>
     </row>
-    <row r="745" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A745" s="7">
         <v>40148</v>
       </c>
@@ -22412,7 +22428,7 @@
       </c>
       <c r="H745" s="10"/>
     </row>
-    <row r="746" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A746" s="7">
         <v>40179</v>
       </c>
@@ -22436,7 +22452,7 @@
       </c>
       <c r="H746" s="10"/>
     </row>
-    <row r="747" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A747" s="7">
         <v>40210</v>
       </c>
@@ -22460,7 +22476,7 @@
       </c>
       <c r="H747" s="10"/>
     </row>
-    <row r="748" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A748" s="7">
         <v>40238</v>
       </c>
@@ -22484,7 +22500,7 @@
       </c>
       <c r="H748" s="10"/>
     </row>
-    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A749" s="7">
         <v>40269</v>
       </c>
@@ -22508,7 +22524,7 @@
       </c>
       <c r="H749" s="10"/>
     </row>
-    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A750" s="7">
         <v>40299</v>
       </c>
@@ -22532,7 +22548,7 @@
       </c>
       <c r="H750" s="10"/>
     </row>
-    <row r="751" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A751" s="7">
         <v>40330</v>
       </c>
@@ -22556,7 +22572,7 @@
       </c>
       <c r="H751" s="10"/>
     </row>
-    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A752" s="7">
         <v>40360</v>
       </c>
@@ -22580,7 +22596,7 @@
       </c>
       <c r="H752" s="10"/>
     </row>
-    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A753" s="7">
         <v>40391</v>
       </c>
@@ -22604,7 +22620,7 @@
       </c>
       <c r="H753" s="10"/>
     </row>
-    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A754" s="7">
         <v>40422</v>
       </c>
@@ -22628,7 +22644,7 @@
       </c>
       <c r="H754" s="10"/>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A755" s="7">
         <v>40452</v>
       </c>
@@ -22652,7 +22668,7 @@
       </c>
       <c r="H755" s="10"/>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A756" s="7">
         <v>40483</v>
       </c>
@@ -22676,7 +22692,7 @@
       </c>
       <c r="H756" s="10"/>
     </row>
-    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A757" s="7">
         <v>40513</v>
       </c>
@@ -22700,7 +22716,7 @@
       </c>
       <c r="H757" s="10"/>
     </row>
-    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A758" s="7">
         <v>40544</v>
       </c>
@@ -22724,7 +22740,7 @@
       </c>
       <c r="H758" s="10"/>
     </row>
-    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A759" s="7">
         <v>40575</v>
       </c>
@@ -22748,7 +22764,7 @@
       </c>
       <c r="H759" s="10"/>
     </row>
-    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A760" s="7">
         <v>40603</v>
       </c>
@@ -22772,7 +22788,7 @@
       </c>
       <c r="H760" s="10"/>
     </row>
-    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A761" s="7">
         <v>40634</v>
       </c>
@@ -22796,7 +22812,7 @@
       </c>
       <c r="H761" s="10"/>
     </row>
-    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A762" s="7">
         <v>40664</v>
       </c>
@@ -22820,7 +22836,7 @@
       </c>
       <c r="H762" s="10"/>
     </row>
-    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A763" s="7">
         <v>40695</v>
       </c>
@@ -22844,7 +22860,7 @@
       </c>
       <c r="H763" s="10"/>
     </row>
-    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A764" s="7">
         <v>40725</v>
       </c>
@@ -22868,7 +22884,7 @@
       </c>
       <c r="H764" s="10"/>
     </row>
-    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A765" s="7">
         <v>40756</v>
       </c>
@@ -22892,7 +22908,7 @@
       </c>
       <c r="H765" s="10"/>
     </row>
-    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A766" s="7">
         <v>40787</v>
       </c>
@@ -22916,7 +22932,7 @@
       </c>
       <c r="H766" s="10"/>
     </row>
-    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A767" s="7">
         <v>40817</v>
       </c>
@@ -22940,7 +22956,7 @@
       </c>
       <c r="H767" s="10"/>
     </row>
-    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A768" s="7">
         <v>40848</v>
       </c>
@@ -22964,7 +22980,7 @@
       </c>
       <c r="H768" s="10"/>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A769" s="7">
         <v>40878</v>
       </c>
@@ -22988,7 +23004,7 @@
       </c>
       <c r="H769" s="10"/>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A770" s="7">
         <v>40909</v>
       </c>
@@ -23012,7 +23028,7 @@
       </c>
       <c r="H770" s="10"/>
     </row>
-    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A771" s="7">
         <v>40940</v>
       </c>
@@ -23036,7 +23052,7 @@
       </c>
       <c r="H771" s="10"/>
     </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A772" s="7">
         <v>40969</v>
       </c>
@@ -23060,7 +23076,7 @@
       </c>
       <c r="H772" s="10"/>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A773" s="7">
         <v>41000</v>
       </c>
@@ -23084,7 +23100,7 @@
       </c>
       <c r="H773" s="10"/>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A774" s="7">
         <v>41030</v>
       </c>
@@ -23108,7 +23124,7 @@
       </c>
       <c r="H774" s="10"/>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A775" s="7">
         <v>41061</v>
       </c>
@@ -23132,7 +23148,7 @@
       </c>
       <c r="H775" s="10"/>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A776" s="7">
         <v>41091</v>
       </c>
@@ -23156,7 +23172,7 @@
       </c>
       <c r="H776" s="10"/>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A777" s="7">
         <v>41122</v>
       </c>
@@ -23180,7 +23196,7 @@
       </c>
       <c r="H777" s="10"/>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A778" s="7">
         <v>41153</v>
       </c>
@@ -23204,7 +23220,7 @@
       </c>
       <c r="H778" s="10"/>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A779" s="7">
         <v>41183</v>
       </c>
@@ -23228,7 +23244,7 @@
       </c>
       <c r="H779" s="10"/>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A780" s="7">
         <v>41214</v>
       </c>
@@ -23252,7 +23268,7 @@
       </c>
       <c r="H780" s="10"/>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A781" s="7">
         <v>41244</v>
       </c>
@@ -23276,7 +23292,7 @@
       </c>
       <c r="H781" s="10"/>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A782" s="7">
         <v>41275</v>
       </c>
@@ -23300,7 +23316,7 @@
       </c>
       <c r="H782" s="10"/>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A783" s="7">
         <v>41306</v>
       </c>
@@ -23324,7 +23340,7 @@
       </c>
       <c r="H783" s="10"/>
     </row>
-    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A784" s="7">
         <v>41334</v>
       </c>
@@ -23348,7 +23364,7 @@
       </c>
       <c r="H784" s="10"/>
     </row>
-    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A785" s="7">
         <v>41365</v>
       </c>
@@ -23372,7 +23388,7 @@
       </c>
       <c r="H785" s="10"/>
     </row>
-    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A786" s="7">
         <v>41395</v>
       </c>
@@ -23396,7 +23412,7 @@
       </c>
       <c r="H786" s="10"/>
     </row>
-    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A787" s="7">
         <v>41426</v>
       </c>
@@ -23420,7 +23436,7 @@
       </c>
       <c r="H787" s="10"/>
     </row>
-    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A788" s="7">
         <v>41456</v>
       </c>
@@ -23443,7 +23459,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A789" s="7">
         <v>41487</v>
       </c>
@@ -23466,7 +23482,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A790" s="7">
         <v>41518</v>
       </c>
@@ -23489,7 +23505,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A791" s="7">
         <v>41548</v>
       </c>
@@ -23512,7 +23528,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A792" s="7">
         <v>41579</v>
       </c>
@@ -23535,7 +23551,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A793" s="7">
         <v>41609</v>
       </c>
@@ -23558,7 +23574,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A794" s="7">
         <v>41640</v>
       </c>
@@ -23581,7 +23597,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A795" s="7">
         <v>41671</v>
       </c>
@@ -23604,7 +23620,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A796" s="7">
         <v>41699</v>
       </c>
@@ -23627,7 +23643,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A797" s="7">
         <v>41730</v>
       </c>
@@ -23650,7 +23666,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A798" s="7">
         <v>41760</v>
       </c>
@@ -23673,7 +23689,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A799" s="7">
         <v>41791</v>
       </c>
@@ -23696,7 +23712,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A800" s="7">
         <v>41821</v>
       </c>
@@ -23719,7 +23735,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A801" s="7">
         <v>41852</v>
       </c>
@@ -23742,7 +23758,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="802" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A802" s="7">
         <v>41883</v>
       </c>
@@ -23765,7 +23781,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A803" s="7">
         <v>41913</v>
       </c>
@@ -23788,7 +23804,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="804" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A804" s="7">
         <v>41944</v>
       </c>
@@ -23811,7 +23827,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A805" s="7">
         <v>41974</v>
       </c>
@@ -23834,7 +23850,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="806" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A806" s="7">
         <v>42005</v>
       </c>
@@ -23857,7 +23873,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A807" s="7">
         <v>42036</v>
       </c>
@@ -23880,7 +23896,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="808" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A808" s="7">
         <v>42064</v>
       </c>
@@ -23903,7 +23919,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A809" s="7">
         <v>42095</v>
       </c>
@@ -23926,7 +23942,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="810" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A810" s="7">
         <v>42125</v>
       </c>
@@ -23949,7 +23965,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A811" s="7">
         <v>42156</v>
       </c>
@@ -23972,7 +23988,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="812" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A812" s="7">
         <v>42186</v>
       </c>
@@ -23995,7 +24011,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="813" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A813" s="7">
         <v>42217</v>
       </c>
@@ -24018,7 +24034,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="814" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A814" s="7">
         <v>42248</v>
       </c>
@@ -24041,7 +24057,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="815" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A815" s="7">
         <v>42278</v>
       </c>
@@ -24064,7 +24080,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="816" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A816" s="7">
         <v>42309</v>
       </c>
@@ -24087,7 +24103,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A817" s="7">
         <v>42339</v>
       </c>
@@ -24110,7 +24126,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A818" s="7">
         <v>42370</v>
       </c>
@@ -24133,7 +24149,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A819" s="7">
         <v>42401</v>
       </c>
@@ -24156,7 +24172,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A820" s="7">
         <v>42430</v>
       </c>
@@ -24179,7 +24195,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A821" s="7">
         <v>42461</v>
       </c>
@@ -24202,7 +24218,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A822" s="7">
         <v>42491</v>
       </c>
@@ -24225,7 +24241,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A823" s="7">
         <v>42522</v>
       </c>
@@ -24248,7 +24264,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A824" s="7">
         <v>42552</v>
       </c>
@@ -24271,7 +24287,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A825" s="7">
         <v>42583</v>
       </c>
@@ -24294,7 +24310,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A826" s="7">
         <v>42614</v>
       </c>
@@ -24317,7 +24333,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A827" s="7">
         <v>42644</v>
       </c>
@@ -24340,7 +24356,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A828" s="7">
         <v>42675</v>
       </c>
@@ -24363,7 +24379,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A829" s="7">
         <v>42705</v>
       </c>
@@ -24386,7 +24402,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A830" s="7">
         <v>42736</v>
       </c>
@@ -24409,7 +24425,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A831" s="7">
         <v>42767</v>
       </c>
@@ -24432,7 +24448,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A832" s="7">
         <v>42795</v>
       </c>
@@ -24455,7 +24471,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A833" s="7">
         <v>42826</v>
       </c>
@@ -24478,7 +24494,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A834" s="7">
         <v>42856</v>
       </c>
@@ -24501,7 +24517,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A835" s="7">
         <v>42887</v>
       </c>
@@ -24524,7 +24540,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A836" s="7">
         <v>42917</v>
       </c>
@@ -24547,7 +24563,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A837" s="7">
         <v>42948</v>
       </c>
@@ -24570,7 +24586,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A838" s="7">
         <v>42979</v>
       </c>
@@ -24593,7 +24609,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A839" s="7">
         <v>43009</v>
       </c>
@@ -24616,7 +24632,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A840" s="7">
         <v>43040</v>
       </c>
@@ -24639,7 +24655,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A841" s="7">
         <v>43070</v>
       </c>
@@ -24662,7 +24678,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A842" s="7">
         <v>43101</v>
       </c>
@@ -24685,7 +24701,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A843" s="7">
         <v>43132</v>
       </c>
@@ -24708,7 +24724,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A844" s="7">
         <v>43160</v>
       </c>
@@ -24731,7 +24747,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A845" s="7">
         <v>43191</v>
       </c>
@@ -24754,7 +24770,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="846" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A846" s="7">
         <v>43221</v>
       </c>
@@ -24777,7 +24793,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A847" s="7">
         <v>43252</v>
       </c>
@@ -24800,7 +24816,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A848" s="7">
         <v>43282</v>
       </c>
@@ -24823,7 +24839,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A849" s="7">
         <v>43313</v>
       </c>
@@ -24846,7 +24862,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="850" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A850" s="7">
         <v>43344</v>
       </c>
@@ -24869,7 +24885,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A851" s="7">
         <v>43374</v>
       </c>
@@ -24892,7 +24908,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="852" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A852" s="7">
         <v>43405</v>
       </c>
@@ -24915,7 +24931,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A853" s="7">
         <v>43435</v>
       </c>
@@ -24938,7 +24954,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="854" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A854" s="7">
         <v>43466</v>
       </c>
@@ -24961,7 +24977,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A855" s="7">
         <v>43497</v>
       </c>
@@ -24984,7 +25000,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="856" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A856" s="7">
         <v>43525</v>
       </c>
@@ -25007,7 +25023,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A857" s="7">
         <v>43556</v>
       </c>
@@ -25030,7 +25046,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="858" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A858" s="7">
         <v>43586</v>
       </c>
@@ -25053,7 +25069,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A859" s="7">
         <v>43617</v>
       </c>
@@ -25076,7 +25092,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="860" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A860" s="7">
         <v>43647</v>
       </c>
@@ -25099,7 +25115,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A861" s="7">
         <v>43678</v>
       </c>
@@ -25122,7 +25138,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="862" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A862" s="7">
         <v>43709</v>
       </c>
@@ -25145,7 +25161,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A863" s="7">
         <v>43739</v>
       </c>
@@ -25168,7 +25184,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="864" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A864" s="7">
         <v>43770</v>
       </c>
@@ -25191,7 +25207,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A865" s="7">
         <v>43800</v>
       </c>
@@ -25214,7 +25230,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A866" s="7">
         <v>43831</v>
       </c>
@@ -25237,7 +25253,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A867" s="7">
         <v>43862</v>
       </c>
@@ -25260,7 +25276,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A868" s="7">
         <v>43891</v>
       </c>
@@ -25283,7 +25299,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A869" s="7">
         <v>43922</v>
       </c>
@@ -25306,7 +25322,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="870" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A870" s="7">
         <v>43952</v>
       </c>
@@ -25329,7 +25345,7 @@
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A871" s="7">
         <v>43983</v>
       </c>
@@ -25352,7 +25368,7 @@
         <v>0.13300000000000001</v>
       </c>
     </row>
-    <row r="872" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A872" s="7">
         <v>44013</v>
       </c>
@@ -25375,7 +25391,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A873" s="7">
         <v>44044</v>
       </c>
@@ -25398,7 +25414,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="874" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A874" s="7">
         <v>44075</v>
       </c>
@@ -25421,7 +25437,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A875" s="7">
         <v>44105</v>
       </c>
@@ -25444,7 +25460,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="876" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A876" s="7">
         <v>44136</v>
       </c>
@@ -25467,7 +25483,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A877" s="7">
         <v>44166</v>
       </c>
@@ -25490,7 +25506,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="878" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A878" s="7">
         <v>44197</v>
       </c>
@@ -25513,7 +25529,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A879" s="7">
         <v>44228</v>
       </c>
@@ -25536,7 +25552,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="880" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A880" s="7">
         <v>44256</v>
       </c>
@@ -25559,7 +25575,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A881" s="7">
         <v>44287</v>
       </c>
@@ -25582,7 +25598,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="882" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A882" s="7">
         <v>44317</v>
       </c>
@@ -25605,7 +25621,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A883" s="7">
         <v>44348</v>
       </c>
@@ -25628,7 +25644,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="884" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A884" s="7">
         <v>44378</v>
       </c>
@@ -25651,7 +25667,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A885" s="7">
         <v>44409</v>
       </c>
@@ -25674,7 +25690,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="886" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A886" s="7">
         <v>44440</v>
       </c>
@@ -25697,7 +25713,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A887" s="7">
         <v>44470</v>
       </c>
@@ -25720,7 +25736,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="888" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A888" s="7">
         <v>44501</v>
       </c>
@@ -25743,7 +25759,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A889" s="7">
         <v>44531</v>
       </c>
@@ -25766,7 +25782,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="890" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A890" s="7">
         <v>44562</v>
       </c>
@@ -25789,7 +25805,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A891" s="7">
         <v>44593</v>
       </c>
@@ -25812,7 +25828,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="892" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A892" s="7">
         <v>44621</v>
       </c>
@@ -25835,7 +25851,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A893" s="7">
         <v>44652</v>
       </c>
@@ -25858,7 +25874,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="894" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A894" s="7">
         <v>44682</v>
       </c>
@@ -25881,7 +25897,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A895" s="7">
         <v>44713</v>
       </c>
@@ -25904,7 +25920,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="896" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A896" s="7">
         <v>44743</v>
       </c>
@@ -25927,7 +25943,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A897" s="7">
         <v>44774</v>
       </c>
@@ -25950,7 +25966,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A898" s="7">
         <v>44805</v>
       </c>
@@ -25973,7 +25989,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A899" s="7">
         <v>44835</v>
       </c>
@@ -25996,7 +26012,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A900" s="7">
         <v>44866</v>
       </c>
@@ -26019,7 +26035,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="901" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A901" s="7">
         <v>44896</v>
       </c>
@@ -26042,7 +26058,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="902" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A902" s="7">
         <v>44927</v>
       </c>
@@ -26065,7 +26081,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="903" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A903" s="7">
         <v>44958</v>
       </c>
@@ -26088,7 +26104,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="904" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A904" s="7">
         <v>44986</v>
       </c>
@@ -26111,7 +26127,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="905" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A905" s="7">
         <v>45017</v>
       </c>
@@ -26134,7 +26150,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="906" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A906" s="7">
         <v>45047</v>
       </c>
@@ -26157,7 +26173,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="907" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A907" s="7">
         <v>45078</v>
       </c>
@@ -26180,7 +26196,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="908" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A908" s="7">
         <v>45108</v>
       </c>
@@ -26203,7 +26219,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="909" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A909" s="7">
         <v>45139</v>
       </c>
@@ -26226,7 +26242,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="910" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A910" s="7">
         <v>45170</v>
       </c>
@@ -26249,7 +26265,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="911" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A911" s="7">
         <v>45200</v>
       </c>
@@ -26272,7 +26288,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="912" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A912" s="7">
         <v>45231</v>
       </c>
@@ -26295,7 +26311,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A913" s="7">
         <v>45261</v>
       </c>
@@ -26318,7 +26334,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="914" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A914" s="7">
         <v>45292</v>
       </c>
@@ -26341,7 +26357,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A915" s="7">
         <v>45323</v>
       </c>
@@ -26364,7 +26380,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="916" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A916" s="7">
         <v>45352</v>
       </c>
@@ -26387,7 +26403,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A917" s="7">
         <v>45383</v>
       </c>
@@ -26410,7 +26426,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="918" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A918" s="7">
         <v>45413</v>
       </c>
@@ -26433,7 +26449,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="919" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A919" s="7">
         <v>45444</v>
       </c>
@@ -26456,7 +26472,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="920" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A920" s="7">
         <v>45474</v>
       </c>
@@ -26479,7 +26495,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="921" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A921" s="7">
         <v>45505</v>
       </c>
@@ -26502,7 +26518,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="922" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A922" s="7">
         <v>45536</v>
       </c>
@@ -26525,7 +26541,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="923" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A923" s="7">
         <v>45566</v>
       </c>
@@ -26548,7 +26564,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="924" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A924" s="7">
         <v>45597</v>
       </c>
@@ -26571,7 +26587,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="925" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A925" s="7">
         <v>45627</v>
       </c>
@@ -26594,7 +26610,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="926" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A926" s="7">
         <v>45658</v>
       </c>
@@ -26617,7 +26633,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="927" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A927" s="7">
         <v>45689</v>
       </c>
@@ -26640,7 +26656,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="928" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A928" s="7">
         <v>45717</v>
       </c>
@@ -26663,7 +26679,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="929" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A929" s="7">
         <v>45748</v>
       </c>
@@ -26686,7 +26702,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="930" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A930" s="7">
         <v>45778</v>
       </c>
@@ -26709,7 +26725,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="931" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A931" s="7">
         <v>45809</v>
       </c>
@@ -26732,7 +26748,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="932" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A932" s="7">
         <v>45839</v>
       </c>
@@ -26755,7 +26771,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="933" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A933" s="7">
         <v>45870</v>
       </c>
@@ -26778,7 +26794,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="934" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A934" s="7">
         <v>45901</v>
       </c>
@@ -26801,7 +26817,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="935" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A935" s="7">
         <v>45962</v>
       </c>
@@ -26824,7 +26840,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="936" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A936" s="7">
         <v>45992</v>
       </c>
@@ -26847,7 +26863,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="937" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A937" s="7">
         <v>46023</v>
       </c>
@@ -26870,7 +26886,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="938" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A938" s="7">
         <v>46054</v>
       </c>
@@ -26891,6 +26907,29 @@
       </c>
       <c r="G938" s="9">
         <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="939" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A939" s="7">
+        <v>46082</v>
+      </c>
+      <c r="B939" s="7">
+        <v>46115</v>
+      </c>
+      <c r="C939" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D939" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E939" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="F939" s="9">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="G939" s="9">
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -26903,7 +26942,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63624C48-49F6-45B9-A627-4576E9CBFBE4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26914,29 +26953,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA19B7F8-4183-46E9-B189-03FA54B61813}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{99673ADB-99EA-46BC-86CB-05CDFA37E542}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>